--- a/docs/data/jp/xlsx/4973.xlsx
+++ b/docs/data/jp/xlsx/4973.xlsx
@@ -12557,7 +12557,7 @@
     <row r="112">
       <c r="A112" s="20" t="inlineStr">
         <is>
-          <t>Accounts Payable Facilities</t>
+          <t>설비관련 미지급금</t>
         </is>
       </c>
       <c r="F112" s="22" t="n">

--- a/docs/data/jp/xlsx/4973.xlsx
+++ b/docs/data/jp/xlsx/4973.xlsx
@@ -201,7 +201,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -323,6 +323,9 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -717,7 +720,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AC141"/>
+  <dimension ref="A1:AC147"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -4317,10 +4320,12 @@
     <row r="47">
       <c r="A47" s="20" t="inlineStr">
         <is>
-          <t>현재 주가 ()</t>
-        </is>
-      </c>
-      <c r="B47" s="29" t="n"/>
+          <t>현재 주가 (2026.10.26)</t>
+        </is>
+      </c>
+      <c r="B47" s="29" t="n">
+        <v>4200</v>
+      </c>
       <c r="C47" s="30" t="n"/>
       <c r="D47" s="31" t="n"/>
       <c r="E47" s="31" t="n"/>
@@ -4355,7 +4360,9 @@
           <t>발행주식수 (보통주)</t>
         </is>
       </c>
-      <c r="B48" s="29" t="n"/>
+      <c r="B48" s="29" t="n">
+        <v>6067200</v>
+      </c>
       <c r="C48" s="30" t="n"/>
       <c r="D48" s="31" t="n"/>
       <c r="E48" s="31" t="n"/>
@@ -5554,7 +5561,7 @@
     <row r="74">
       <c r="A74" s="43" t="inlineStr">
         <is>
-          <t>주가: 야후 파이낸스 일봉</t>
+          <t>주가: 야후 파이낸스 일봉 2026.10.26</t>
         </is>
       </c>
       <c r="C74" s="41" t="n"/>
@@ -5806,934 +5813,1016 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="20" t="inlineStr">
+      <c r="A79" s="45" t="inlineStr">
+        <is>
+          <t>YoY</t>
+        </is>
+      </c>
+      <c r="B79" s="3" t="inlineStr">
+        <is>
+          <t>전년 같은 분기·전년 대비</t>
+        </is>
+      </c>
+      <c r="G79" s="17">
+        <f>IF(OR(G78="",C78=""),"",IF(C78&lt;=0,"",IFERROR(G78/C78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="H79" s="17">
+        <f>IF(OR(H78="",D78=""),"",IF(D78&lt;=0,"",IFERROR(H78/D78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="I79" s="17">
+        <f>IF(OR(I78="",E78=""),"",IF(E78&lt;=0,"",IFERROR(I78/E78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="J79" s="17">
+        <f>IF(OR(J78="",F78=""),"",IF(F78&lt;=0,"",IFERROR(J78/F78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="K79" s="17">
+        <f>IF(OR(K78="",G78=""),"",IF(G78&lt;=0,"",IFERROR(K78/G78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="L79" s="17">
+        <f>IF(OR(L78="",H78=""),"",IF(H78&lt;=0,"",IFERROR(L78/H78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="M79" s="17">
+        <f>IF(OR(M78="",I78=""),"",IF(I78&lt;=0,"",IFERROR(M78/I78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="N79" s="17">
+        <f>IF(OR(N78="",J78=""),"",IF(J78&lt;=0,"",IFERROR(N78/J78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="T79" s="17">
+        <f>IF(OR(T78="",S78=""),"",IF(S78&lt;=0,"",IFERROR(T78/S78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="U79" s="17">
+        <f>IF(OR(U78="",T78=""),"",IF(T78&lt;=0,"",IFERROR(U78/T78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="V79" s="17">
+        <f>IF(OR(V78="",U78=""),"",IF(U78&lt;=0,"",IFERROR(V78/U78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="W79" s="17">
+        <f>IF(OR(W78="",V78=""),"",IF(V78&lt;=0,"",IFERROR(W78/V78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="X79" s="17">
+        <f>IF(OR(X78="",W78=""),"",IF(W78&lt;=0,"",IFERROR(X78/W78-1,"")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="20" t="inlineStr">
         <is>
           <t>매출원가</t>
         </is>
       </c>
-      <c r="C79" s="22" t="n">
+      <c r="C80" s="22" t="n">
         <v>2843.727</v>
       </c>
-      <c r="D79" s="22" t="n">
+      <c r="D80" s="22" t="n">
         <v>2299.257</v>
       </c>
-      <c r="F79" s="22" t="n">
+      <c r="F80" s="22" t="n">
         <v>2649.489</v>
       </c>
-      <c r="G79" s="22" t="n">
+      <c r="G80" s="22" t="n">
         <v>2849.672</v>
       </c>
-      <c r="H79" s="22" t="n">
+      <c r="H80" s="22" t="n">
         <v>3302.831</v>
       </c>
-      <c r="J79" s="22" t="n">
+      <c r="J80" s="22" t="n">
         <v>3000.458</v>
       </c>
-      <c r="K79" s="22" t="n">
+      <c r="K80" s="22" t="n">
         <v>3629.392</v>
       </c>
-      <c r="L79" s="22" t="n">
+      <c r="L80" s="22" t="n">
         <v>4198.023</v>
       </c>
-      <c r="N79" s="22" t="n">
+      <c r="N80" s="22" t="n">
         <v>5763.505</v>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" s="9" t="inlineStr">
+    <row r="81">
+      <c r="A81" s="9" t="inlineStr">
         <is>
           <t>매출총이익</t>
         </is>
       </c>
-      <c r="C80" s="12" t="n">
+      <c r="C81" s="12" t="n">
         <v>355.608</v>
       </c>
-      <c r="D80" s="12" t="n">
+      <c r="D81" s="12" t="n">
         <v>379.795</v>
       </c>
-      <c r="E80" s="12" t="n">
+      <c r="E81" s="12" t="n">
         <v>328.758</v>
       </c>
-      <c r="F80" s="12" t="n">
+      <c r="F81" s="12" t="n">
         <v>429.55</v>
       </c>
-      <c r="G80" s="12" t="n">
+      <c r="G81" s="12" t="n">
         <v>401.523</v>
       </c>
-      <c r="H80" s="12" t="n">
+      <c r="H81" s="12" t="n">
         <v>428.647</v>
       </c>
-      <c r="I80" s="12" t="n">
+      <c r="I81" s="12" t="n">
         <v>368.796</v>
       </c>
-      <c r="J80" s="12" t="n">
+      <c r="J81" s="12" t="n">
         <v>406.536</v>
       </c>
-      <c r="K80" s="12" t="n">
+      <c r="K81" s="12" t="n">
         <v>499.755</v>
       </c>
-      <c r="L80" s="12" t="n">
+      <c r="L81" s="12" t="n">
         <v>532.895</v>
       </c>
-      <c r="M80" s="12" t="n">
+      <c r="M81" s="12" t="n">
         <v>499.169</v>
       </c>
-      <c r="N80" s="12" t="n">
+      <c r="N81" s="12" t="n">
         <v>389.308</v>
       </c>
-      <c r="T80" s="12" t="n">
+      <c r="T81" s="12" t="n">
         <v>559.287</v>
       </c>
-      <c r="U80" s="12" t="n">
+      <c r="U81" s="12" t="n">
         <v>296.733</v>
       </c>
-      <c r="V80" s="12" t="n">
+      <c r="V81" s="12" t="n">
         <v>328.758</v>
       </c>
-      <c r="W80" s="12" t="n">
+      <c r="W81" s="12" t="n">
         <v>368.796</v>
       </c>
-      <c r="X80" s="12" t="n">
+      <c r="X81" s="12" t="n">
         <v>499.169</v>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" s="20" t="inlineStr">
-        <is>
-          <t>판매비와 관리비</t>
-        </is>
-      </c>
-      <c r="C81" s="22" t="n">
-        <v>257.253</v>
-      </c>
-      <c r="D81" s="22" t="n">
-        <v>247.748</v>
-      </c>
-      <c r="E81" s="22" t="n">
-        <v>259.492</v>
-      </c>
-      <c r="F81" s="22" t="n">
-        <v>280.127</v>
-      </c>
-      <c r="G81" s="22" t="n">
-        <v>284.446</v>
-      </c>
-      <c r="H81" s="22" t="n">
-        <v>277.752</v>
-      </c>
-      <c r="I81" s="22" t="n">
-        <v>283.542</v>
-      </c>
-      <c r="J81" s="22" t="n">
-        <v>313.563</v>
-      </c>
-      <c r="K81" s="22" t="n">
-        <v>321.246</v>
-      </c>
-      <c r="L81" s="22" t="n">
-        <v>366.818</v>
-      </c>
-      <c r="M81" s="22" t="n">
-        <v>360.352</v>
-      </c>
-      <c r="N81" s="22" t="n">
-        <v>357.983</v>
-      </c>
-      <c r="T81" s="22" t="n">
-        <v>241.445</v>
-      </c>
-      <c r="U81" s="22" t="n">
-        <v>243.485</v>
-      </c>
-      <c r="V81" s="22" t="n">
-        <v>259.492</v>
-      </c>
-      <c r="W81" s="22" t="n">
-        <v>283.542</v>
-      </c>
-      <c r="X81" s="22" t="n">
-        <v>360.352</v>
-      </c>
-    </row>
     <row r="82">
-      <c r="A82" s="9" t="inlineStr">
-        <is>
-          <t>영업이익</t>
-        </is>
-      </c>
-      <c r="C82" s="12" t="n">
-        <v>98.355</v>
-      </c>
-      <c r="D82" s="12" t="n">
-        <v>132.046</v>
-      </c>
-      <c r="E82" s="12" t="n">
-        <v>69.267</v>
-      </c>
-      <c r="F82" s="12" t="n">
-        <v>149.423</v>
-      </c>
-      <c r="G82" s="12" t="n">
-        <v>117.076</v>
-      </c>
-      <c r="H82" s="12" t="n">
-        <v>150.895</v>
-      </c>
-      <c r="I82" s="12" t="n">
-        <v>85.254</v>
-      </c>
-      <c r="J82" s="12" t="n">
-        <v>92.97199999999999</v>
-      </c>
-      <c r="K82" s="12" t="n">
-        <v>178.509</v>
-      </c>
-      <c r="L82" s="12" t="n">
-        <v>166.077</v>
-      </c>
-      <c r="M82" s="12" t="n">
-        <v>138.817</v>
-      </c>
-      <c r="N82" s="12" t="n">
-        <v>31.324</v>
-      </c>
-      <c r="T82" s="12" t="n">
-        <v>317.842</v>
-      </c>
-      <c r="U82" s="12" t="n">
-        <v>53.248</v>
-      </c>
-      <c r="V82" s="12" t="n">
-        <v>69.267</v>
-      </c>
-      <c r="W82" s="12" t="n">
-        <v>85.254</v>
-      </c>
-      <c r="X82" s="12" t="n">
-        <v>138.817</v>
+      <c r="A82" s="45" t="inlineStr">
+        <is>
+          <t>YoY</t>
+        </is>
+      </c>
+      <c r="B82" s="3" t="inlineStr">
+        <is>
+          <t>전년 같은 분기·전년 대비</t>
+        </is>
+      </c>
+      <c r="G82" s="17">
+        <f>IF(OR(G81="",C81=""),"",IF(C81&lt;=0,"",IFERROR(G81/C81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="H82" s="17">
+        <f>IF(OR(H81="",D81=""),"",IF(D81&lt;=0,"",IFERROR(H81/D81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="I82" s="17">
+        <f>IF(OR(I81="",E81=""),"",IF(E81&lt;=0,"",IFERROR(I81/E81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="J82" s="17">
+        <f>IF(OR(J81="",F81=""),"",IF(F81&lt;=0,"",IFERROR(J81/F81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="K82" s="17">
+        <f>IF(OR(K81="",G81=""),"",IF(G81&lt;=0,"",IFERROR(K81/G81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="L82" s="17">
+        <f>IF(OR(L81="",H81=""),"",IF(H81&lt;=0,"",IFERROR(L81/H81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="M82" s="17">
+        <f>IF(OR(M81="",I81=""),"",IF(I81&lt;=0,"",IFERROR(M81/I81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="N82" s="17">
+        <f>IF(OR(N81="",J81=""),"",IF(J81&lt;=0,"",IFERROR(N81/J81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="T82" s="17">
+        <f>IF(OR(T81="",S81=""),"",IF(S81&lt;=0,"",IFERROR(T81/S81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="U82" s="17">
+        <f>IF(OR(U81="",T81=""),"",IF(T81&lt;=0,"",IFERROR(U81/T81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="V82" s="17">
+        <f>IF(OR(V81="",U81=""),"",IF(U81&lt;=0,"",IFERROR(V81/U81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="W82" s="17">
+        <f>IF(OR(W81="",V81=""),"",IF(V81&lt;=0,"",IFERROR(W81/V81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="X82" s="17">
+        <f>IF(OR(X81="",W81=""),"",IF(W81&lt;=0,"",IFERROR(X81/W81-1,"")))</f>
+        <v/>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="20" t="inlineStr">
         <is>
-          <t>이자수익</t>
+          <t>판매비와 관리비</t>
         </is>
       </c>
       <c r="C83" s="22" t="n">
-        <v>0.027</v>
+        <v>257.253</v>
       </c>
       <c r="D83" s="22" t="n">
-        <v>0.003</v>
+        <v>247.748</v>
       </c>
       <c r="E83" s="22" t="n">
-        <v>0.027</v>
+        <v>259.492</v>
       </c>
       <c r="F83" s="22" t="n">
-        <v>0.003</v>
+        <v>280.127</v>
       </c>
       <c r="G83" s="22" t="n">
-        <v>0.434</v>
+        <v>284.446</v>
       </c>
       <c r="H83" s="22" t="n">
-        <v>0.037</v>
+        <v>277.752</v>
       </c>
       <c r="I83" s="22" t="n">
-        <v>3.055</v>
+        <v>283.542</v>
       </c>
       <c r="J83" s="22" t="n">
-        <v>0.186</v>
+        <v>313.563</v>
       </c>
       <c r="K83" s="22" t="n">
-        <v>6.346</v>
+        <v>321.246</v>
       </c>
       <c r="L83" s="22" t="n">
-        <v>0.376</v>
+        <v>366.818</v>
       </c>
       <c r="M83" s="22" t="n">
-        <v>7.183</v>
+        <v>360.352</v>
       </c>
       <c r="N83" s="22" t="n">
-        <v>0.373</v>
+        <v>357.983</v>
       </c>
       <c r="T83" s="22" t="n">
-        <v>0.018</v>
+        <v>241.445</v>
       </c>
       <c r="U83" s="22" t="n">
-        <v>0.021</v>
+        <v>243.485</v>
       </c>
       <c r="V83" s="22" t="n">
-        <v>0.027</v>
+        <v>259.492</v>
       </c>
       <c r="W83" s="22" t="n">
-        <v>3.055</v>
+        <v>283.542</v>
       </c>
       <c r="X83" s="22" t="n">
-        <v>7.183</v>
+        <v>360.352</v>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="20" t="inlineStr">
-        <is>
-          <t>배당금수익</t>
-        </is>
-      </c>
-      <c r="C84" s="22" t="n">
-        <v>8.738</v>
-      </c>
-      <c r="D84" s="22" t="n">
-        <v>84.57299999999999</v>
-      </c>
-      <c r="E84" s="22" t="n">
-        <v>4.663</v>
-      </c>
-      <c r="F84" s="22" t="n">
-        <v>90.96299999999999</v>
-      </c>
-      <c r="G84" s="22" t="n">
-        <v>8.077</v>
-      </c>
-      <c r="H84" s="22" t="n">
-        <v>83.024</v>
-      </c>
-      <c r="I84" s="22" t="n">
-        <v>6</v>
-      </c>
-      <c r="J84" s="22" t="n">
-        <v>90.782</v>
-      </c>
-      <c r="K84" s="22" t="n">
-        <v>12.837</v>
-      </c>
-      <c r="L84" s="22" t="n">
-        <v>89.776</v>
-      </c>
-      <c r="M84" s="22" t="n">
-        <v>10.685</v>
-      </c>
-      <c r="N84" s="22" t="n">
-        <v>90.065</v>
-      </c>
-      <c r="T84" s="22" t="n">
-        <v>2.429</v>
-      </c>
-      <c r="U84" s="22" t="n">
-        <v>4.508</v>
-      </c>
-      <c r="V84" s="22" t="n">
-        <v>4.663</v>
-      </c>
-      <c r="W84" s="22" t="n">
-        <v>6</v>
-      </c>
-      <c r="X84" s="22" t="n">
-        <v>10.685</v>
+      <c r="A84" s="9" t="inlineStr">
+        <is>
+          <t>영업이익</t>
+        </is>
+      </c>
+      <c r="C84" s="12" t="n">
+        <v>98.355</v>
+      </c>
+      <c r="D84" s="12" t="n">
+        <v>132.046</v>
+      </c>
+      <c r="E84" s="12" t="n">
+        <v>69.267</v>
+      </c>
+      <c r="F84" s="12" t="n">
+        <v>149.423</v>
+      </c>
+      <c r="G84" s="12" t="n">
+        <v>117.076</v>
+      </c>
+      <c r="H84" s="12" t="n">
+        <v>150.895</v>
+      </c>
+      <c r="I84" s="12" t="n">
+        <v>85.254</v>
+      </c>
+      <c r="J84" s="12" t="n">
+        <v>92.97199999999999</v>
+      </c>
+      <c r="K84" s="12" t="n">
+        <v>178.509</v>
+      </c>
+      <c r="L84" s="12" t="n">
+        <v>166.077</v>
+      </c>
+      <c r="M84" s="12" t="n">
+        <v>138.817</v>
+      </c>
+      <c r="N84" s="12" t="n">
+        <v>31.324</v>
+      </c>
+      <c r="T84" s="12" t="n">
+        <v>317.842</v>
+      </c>
+      <c r="U84" s="12" t="n">
+        <v>53.248</v>
+      </c>
+      <c r="V84" s="12" t="n">
+        <v>69.267</v>
+      </c>
+      <c r="W84" s="12" t="n">
+        <v>85.254</v>
+      </c>
+      <c r="X84" s="12" t="n">
+        <v>138.817</v>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="20" t="inlineStr">
-        <is>
-          <t>외환차익</t>
-        </is>
-      </c>
-      <c r="C85" s="22" t="n">
-        <v>0.497</v>
-      </c>
-      <c r="D85" s="22" t="n">
-        <v>-0.597</v>
-      </c>
-      <c r="E85" s="22" t="n">
-        <v>0.577</v>
-      </c>
-      <c r="F85" s="22" t="n">
-        <v>0.794</v>
-      </c>
-      <c r="G85" s="22" t="n">
-        <v>-0.794</v>
-      </c>
-      <c r="H85" s="22" t="n">
-        <v>0.427</v>
-      </c>
-      <c r="I85" s="22" t="n">
-        <v>-0.427</v>
-      </c>
-      <c r="J85" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K85" s="22" t="n">
-        <v>0.234</v>
-      </c>
-      <c r="L85" s="22" t="n">
-        <v>0.576</v>
-      </c>
-      <c r="M85" s="22" t="n">
-        <v>0.256</v>
-      </c>
-      <c r="N85" s="22" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="T85" s="22" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="U85" s="22" t="n">
-        <v>-0.082</v>
-      </c>
-      <c r="V85" s="22" t="n">
-        <v>0.577</v>
-      </c>
-      <c r="W85" s="22" t="n">
-        <v>-0.427</v>
-      </c>
-      <c r="X85" s="22" t="n">
-        <v>0.256</v>
+      <c r="A85" s="45" t="inlineStr">
+        <is>
+          <t>OPM</t>
+        </is>
+      </c>
+      <c r="B85" s="3" t="inlineStr">
+        <is>
+          <t>영업이익 ÷ 매출</t>
+        </is>
+      </c>
+      <c r="C85" s="17">
+        <f>IF(OR(C84="",C78=""),"",IF(C78&lt;=0,"",IFERROR(C84/C78,"")))</f>
+        <v/>
+      </c>
+      <c r="D85" s="17">
+        <f>IF(OR(D84="",D78=""),"",IF(D78&lt;=0,"",IFERROR(D84/D78,"")))</f>
+        <v/>
+      </c>
+      <c r="E85" s="17">
+        <f>IF(OR(E84="",E78=""),"",IF(E78&lt;=0,"",IFERROR(E84/E78,"")))</f>
+        <v/>
+      </c>
+      <c r="F85" s="17">
+        <f>IF(OR(F84="",F78=""),"",IF(F78&lt;=0,"",IFERROR(F84/F78,"")))</f>
+        <v/>
+      </c>
+      <c r="G85" s="17">
+        <f>IF(OR(G84="",G78=""),"",IF(G78&lt;=0,"",IFERROR(G84/G78,"")))</f>
+        <v/>
+      </c>
+      <c r="H85" s="17">
+        <f>IF(OR(H84="",H78=""),"",IF(H78&lt;=0,"",IFERROR(H84/H78,"")))</f>
+        <v/>
+      </c>
+      <c r="I85" s="17">
+        <f>IF(OR(I84="",I78=""),"",IF(I78&lt;=0,"",IFERROR(I84/I78,"")))</f>
+        <v/>
+      </c>
+      <c r="J85" s="17">
+        <f>IF(OR(J84="",J78=""),"",IF(J78&lt;=0,"",IFERROR(J84/J78,"")))</f>
+        <v/>
+      </c>
+      <c r="K85" s="17">
+        <f>IF(OR(K84="",K78=""),"",IF(K78&lt;=0,"",IFERROR(K84/K78,"")))</f>
+        <v/>
+      </c>
+      <c r="L85" s="17">
+        <f>IF(OR(L84="",L78=""),"",IF(L78&lt;=0,"",IFERROR(L84/L78,"")))</f>
+        <v/>
+      </c>
+      <c r="M85" s="17">
+        <f>IF(OR(M84="",M78=""),"",IF(M78&lt;=0,"",IFERROR(M84/M78,"")))</f>
+        <v/>
+      </c>
+      <c r="N85" s="17">
+        <f>IF(OR(N84="",N78=""),"",IF(N78&lt;=0,"",IFERROR(N84/N78,"")))</f>
+        <v/>
+      </c>
+      <c r="T85" s="17">
+        <f>IF(OR(T84="",T78=""),"",IF(T78&lt;=0,"",IFERROR(T84/T78,"")))</f>
+        <v/>
+      </c>
+      <c r="U85" s="17">
+        <f>IF(OR(U84="",U78=""),"",IF(U78&lt;=0,"",IFERROR(U84/U78,"")))</f>
+        <v/>
+      </c>
+      <c r="V85" s="17">
+        <f>IF(OR(V84="",V78=""),"",IF(V78&lt;=0,"",IFERROR(V84/V78,"")))</f>
+        <v/>
+      </c>
+      <c r="W85" s="17">
+        <f>IF(OR(W84="",W78=""),"",IF(W78&lt;=0,"",IFERROR(W84/W78,"")))</f>
+        <v/>
+      </c>
+      <c r="X85" s="17">
+        <f>IF(OR(X84="",X78=""),"",IF(X78&lt;=0,"",IFERROR(X84/X78,"")))</f>
+        <v/>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="20" t="inlineStr">
-        <is>
-          <t>기타</t>
-        </is>
-      </c>
-      <c r="C86" s="22" t="n">
-        <v>0.508</v>
-      </c>
-      <c r="D86" s="22" t="n">
-        <v>0.779</v>
-      </c>
-      <c r="F86" s="22" t="n">
-        <v>0.435</v>
-      </c>
-      <c r="G86" s="22" t="n">
-        <v>0.245</v>
-      </c>
-      <c r="H86" s="22" t="n">
-        <v>1.224</v>
-      </c>
-      <c r="J86" s="22" t="n">
-        <v>0.745</v>
-      </c>
-      <c r="K86" s="22" t="n">
-        <v>0.357</v>
-      </c>
-      <c r="L86" s="22" t="n">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="N86" s="22" t="n">
-        <v>0.765</v>
+      <c r="A86" s="45" t="inlineStr">
+        <is>
+          <t>YoY</t>
+        </is>
+      </c>
+      <c r="B86" s="3" t="inlineStr">
+        <is>
+          <t>전년 같은 분기·전년 대비</t>
+        </is>
+      </c>
+      <c r="G86" s="17">
+        <f>IF(OR(G84="",C84=""),"",IF(C84&lt;=0,"",IFERROR(G84/C84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="H86" s="17">
+        <f>IF(OR(H84="",D84=""),"",IF(D84&lt;=0,"",IFERROR(H84/D84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="I86" s="17">
+        <f>IF(OR(I84="",E84=""),"",IF(E84&lt;=0,"",IFERROR(I84/E84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="J86" s="17">
+        <f>IF(OR(J84="",F84=""),"",IF(F84&lt;=0,"",IFERROR(J84/F84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="K86" s="17">
+        <f>IF(OR(K84="",G84=""),"",IF(G84&lt;=0,"",IFERROR(K84/G84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="L86" s="17">
+        <f>IF(OR(L84="",H84=""),"",IF(H84&lt;=0,"",IFERROR(L84/H84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="M86" s="17">
+        <f>IF(OR(M84="",I84=""),"",IF(I84&lt;=0,"",IFERROR(M84/I84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="N86" s="17">
+        <f>IF(OR(N84="",J84=""),"",IF(J84&lt;=0,"",IFERROR(N84/J84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="T86" s="17">
+        <f>IF(OR(T84="",S84=""),"",IF(S84&lt;=0,"",IFERROR(T84/S84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="U86" s="17">
+        <f>IF(OR(U84="",T84=""),"",IF(T84&lt;=0,"",IFERROR(U84/T84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="V86" s="17">
+        <f>IF(OR(V84="",U84=""),"",IF(U84&lt;=0,"",IFERROR(V84/U84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="W86" s="17">
+        <f>IF(OR(W84="",V84=""),"",IF(V84&lt;=0,"",IFERROR(W84/V84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="X86" s="17">
+        <f>IF(OR(X84="",W84=""),"",IF(W84&lt;=0,"",IFERROR(X84/W84-1,"")))</f>
+        <v/>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="20" t="inlineStr">
         <is>
-          <t>영업외수익 합계</t>
+          <t>이자수익</t>
         </is>
       </c>
       <c r="C87" s="22" t="n">
-        <v>9.768000000000001</v>
+        <v>0.027</v>
       </c>
       <c r="D87" s="22" t="n">
-        <v>84.759</v>
+        <v>0.003</v>
       </c>
       <c r="E87" s="22" t="n">
-        <v>5.451</v>
+        <v>0.027</v>
       </c>
       <c r="F87" s="22" t="n">
-        <v>92.196</v>
+        <v>0.003</v>
       </c>
       <c r="G87" s="22" t="n">
-        <v>7.962</v>
+        <v>0.434</v>
       </c>
       <c r="H87" s="22" t="n">
-        <v>84.71299999999999</v>
+        <v>0.037</v>
       </c>
       <c r="I87" s="22" t="n">
-        <v>9.191000000000001</v>
+        <v>3.055</v>
       </c>
       <c r="J87" s="22" t="n">
-        <v>91.714</v>
+        <v>0.186</v>
       </c>
       <c r="K87" s="22" t="n">
-        <v>19.775</v>
+        <v>6.346</v>
       </c>
       <c r="L87" s="22" t="n">
-        <v>91.417</v>
+        <v>0.376</v>
       </c>
       <c r="M87" s="22" t="n">
-        <v>18.638</v>
+        <v>7.183</v>
       </c>
       <c r="N87" s="22" t="n">
-        <v>91.55500000000001</v>
+        <v>0.373</v>
       </c>
       <c r="T87" s="22" t="n">
-        <v>4.141</v>
+        <v>0.018</v>
       </c>
       <c r="U87" s="22" t="n">
-        <v>4.892</v>
+        <v>0.021</v>
       </c>
       <c r="V87" s="22" t="n">
-        <v>5.451</v>
+        <v>0.027</v>
       </c>
       <c r="W87" s="22" t="n">
-        <v>9.191000000000001</v>
+        <v>3.055</v>
       </c>
       <c r="X87" s="22" t="n">
-        <v>18.638</v>
+        <v>7.183</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="20" t="inlineStr">
         <is>
-          <t>지급수수료</t>
-        </is>
+          <t>배당금수익</t>
+        </is>
+      </c>
+      <c r="C88" s="22" t="n">
+        <v>8.738</v>
       </c>
       <c r="D88" s="22" t="n">
-        <v>0</v>
+        <v>84.57299999999999</v>
       </c>
       <c r="E88" s="22" t="n">
-        <v>0.534</v>
+        <v>4.663</v>
+      </c>
+      <c r="F88" s="22" t="n">
+        <v>90.96299999999999</v>
+      </c>
+      <c r="G88" s="22" t="n">
+        <v>8.077</v>
       </c>
       <c r="H88" s="22" t="n">
-        <v>32.592</v>
+        <v>83.024</v>
       </c>
       <c r="I88" s="22" t="n">
-        <v>0.226</v>
+        <v>6</v>
+      </c>
+      <c r="J88" s="22" t="n">
+        <v>90.782</v>
+      </c>
+      <c r="K88" s="22" t="n">
+        <v>12.837</v>
       </c>
       <c r="L88" s="22" t="n">
-        <v>15.305</v>
+        <v>89.776</v>
       </c>
       <c r="M88" s="22" t="n">
-        <v>1.58</v>
+        <v>10.685</v>
+      </c>
+      <c r="N88" s="22" t="n">
+        <v>90.065</v>
+      </c>
+      <c r="T88" s="22" t="n">
+        <v>2.429</v>
+      </c>
+      <c r="U88" s="22" t="n">
+        <v>4.508</v>
       </c>
       <c r="V88" s="22" t="n">
-        <v>0.534</v>
+        <v>4.663</v>
       </c>
       <c r="W88" s="22" t="n">
-        <v>0.226</v>
+        <v>6</v>
       </c>
       <c r="X88" s="22" t="n">
-        <v>1.58</v>
+        <v>10.685</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="20" t="inlineStr">
         <is>
-          <t>외환차손</t>
-        </is>
+          <t>외환차익</t>
+        </is>
+      </c>
+      <c r="C89" s="22" t="n">
+        <v>0.497</v>
+      </c>
+      <c r="D89" s="22" t="n">
+        <v>-0.597</v>
+      </c>
+      <c r="E89" s="22" t="n">
+        <v>0.577</v>
       </c>
       <c r="F89" s="22" t="n">
+        <v>0.794</v>
+      </c>
+      <c r="G89" s="22" t="n">
+        <v>-0.794</v>
+      </c>
+      <c r="H89" s="22" t="n">
+        <v>0.427</v>
+      </c>
+      <c r="I89" s="22" t="n">
+        <v>-0.427</v>
+      </c>
+      <c r="J89" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="G89" s="22" t="n">
-        <v>0.637</v>
-      </c>
-      <c r="J89" s="22" t="n">
-        <v>0.17</v>
-      </c>
       <c r="K89" s="22" t="n">
-        <v>-0.17</v>
+        <v>0.234</v>
+      </c>
+      <c r="L89" s="22" t="n">
+        <v>0.576</v>
+      </c>
+      <c r="M89" s="22" t="n">
+        <v>0.256</v>
       </c>
       <c r="N89" s="22" t="n">
-        <v>0</v>
+        <v>0.35</v>
+      </c>
+      <c r="T89" s="22" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="U89" s="22" t="n">
+        <v>-0.082</v>
+      </c>
+      <c r="V89" s="22" t="n">
+        <v>0.577</v>
+      </c>
+      <c r="W89" s="22" t="n">
+        <v>-0.427</v>
+      </c>
+      <c r="X89" s="22" t="n">
+        <v>0.256</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="20" t="inlineStr">
         <is>
-          <t>잡손실</t>
-        </is>
-      </c>
-      <c r="E90" s="22" t="n">
-        <v>0.534</v>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="C90" s="22" t="n">
+        <v>0.508</v>
+      </c>
+      <c r="D90" s="22" t="n">
+        <v>0.779</v>
       </c>
       <c r="F90" s="22" t="n">
-        <v>0.213</v>
+        <v>0.435</v>
+      </c>
+      <c r="G90" s="22" t="n">
+        <v>0.245</v>
+      </c>
+      <c r="H90" s="22" t="n">
+        <v>1.224</v>
       </c>
       <c r="J90" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="T90" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="U90" s="22" t="n">
-        <v>0.884</v>
-      </c>
-      <c r="V90" s="22" t="n">
-        <v>0.534</v>
+        <v>0.745</v>
+      </c>
+      <c r="K90" s="22" t="n">
+        <v>0.357</v>
+      </c>
+      <c r="L90" s="22" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="N90" s="22" t="n">
+        <v>0.765</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="20" t="inlineStr">
         <is>
-          <t>영업외비용 합계</t>
+          <t>영업외수익 합계</t>
         </is>
       </c>
       <c r="C91" s="22" t="n">
+        <v>9.768000000000001</v>
+      </c>
+      <c r="D91" s="22" t="n">
+        <v>84.759</v>
+      </c>
+      <c r="E91" s="22" t="n">
+        <v>5.451</v>
+      </c>
+      <c r="F91" s="22" t="n">
+        <v>92.196</v>
+      </c>
+      <c r="G91" s="22" t="n">
+        <v>7.962</v>
+      </c>
+      <c r="H91" s="22" t="n">
+        <v>84.71299999999999</v>
+      </c>
+      <c r="I91" s="22" t="n">
+        <v>9.191000000000001</v>
+      </c>
+      <c r="J91" s="22" t="n">
+        <v>91.714</v>
+      </c>
+      <c r="K91" s="22" t="n">
+        <v>19.775</v>
+      </c>
+      <c r="L91" s="22" t="n">
+        <v>91.417</v>
+      </c>
+      <c r="M91" s="22" t="n">
+        <v>18.638</v>
+      </c>
+      <c r="N91" s="22" t="n">
+        <v>91.55500000000001</v>
+      </c>
+      <c r="T91" s="22" t="n">
+        <v>4.141</v>
+      </c>
+      <c r="U91" s="22" t="n">
+        <v>4.892</v>
+      </c>
+      <c r="V91" s="22" t="n">
+        <v>5.451</v>
+      </c>
+      <c r="W91" s="22" t="n">
+        <v>9.191000000000001</v>
+      </c>
+      <c r="X91" s="22" t="n">
+        <v>18.638</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="20" t="inlineStr">
+        <is>
+          <t>지급수수료</t>
+        </is>
+      </c>
+      <c r="D92" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="D91" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E91" s="22" t="n">
+      <c r="E92" s="22" t="n">
         <v>0.534</v>
       </c>
-      <c r="F91" s="22" t="n">
-        <v>0.213</v>
-      </c>
-      <c r="G91" s="22" t="n">
-        <v>6.572</v>
-      </c>
-      <c r="H91" s="22" t="n">
-        <v>31.955</v>
-      </c>
-      <c r="I91" s="22" t="n">
-        <v>0.477</v>
-      </c>
-      <c r="J91" s="22" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="K91" s="22" t="n">
-        <v>4.764</v>
-      </c>
-      <c r="L91" s="22" t="n">
+      <c r="H92" s="22" t="n">
+        <v>32.592</v>
+      </c>
+      <c r="I92" s="22" t="n">
+        <v>0.226</v>
+      </c>
+      <c r="L92" s="22" t="n">
         <v>15.305</v>
       </c>
-      <c r="M91" s="22" t="n">
+      <c r="M92" s="22" t="n">
         <v>1.58</v>
       </c>
-      <c r="N91" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="T91" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="U91" s="22" t="n">
-        <v>0.884</v>
-      </c>
-      <c r="V91" s="22" t="n">
+      <c r="V92" s="22" t="n">
         <v>0.534</v>
       </c>
-      <c r="W91" s="22" t="n">
-        <v>0.477</v>
-      </c>
-      <c r="X91" s="22" t="n">
+      <c r="W92" s="22" t="n">
+        <v>0.226</v>
+      </c>
+      <c r="X92" s="22" t="n">
         <v>1.58</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="9" t="inlineStr">
-        <is>
-          <t>경상이익</t>
-        </is>
-      </c>
-      <c r="C92" s="12" t="n">
-        <v>108.124</v>
-      </c>
-      <c r="D92" s="12" t="n">
-        <v>216.805</v>
-      </c>
-      <c r="E92" s="12" t="n">
-        <v>74.18300000000001</v>
-      </c>
-      <c r="F92" s="12" t="n">
-        <v>241.406</v>
-      </c>
-      <c r="G92" s="12" t="n">
-        <v>118.466</v>
-      </c>
-      <c r="H92" s="12" t="n">
-        <v>203.653</v>
-      </c>
-      <c r="I92" s="12" t="n">
-        <v>93.968</v>
-      </c>
-      <c r="J92" s="12" t="n">
-        <v>184.517</v>
-      </c>
-      <c r="K92" s="12" t="n">
-        <v>193.52</v>
-      </c>
-      <c r="L92" s="12" t="n">
-        <v>242.189</v>
-      </c>
-      <c r="M92" s="12" t="n">
-        <v>155.874</v>
-      </c>
-      <c r="N92" s="12" t="n">
-        <v>122.879</v>
-      </c>
-      <c r="T92" s="12" t="n">
-        <v>321.983</v>
-      </c>
-      <c r="U92" s="12" t="n">
-        <v>57.258</v>
-      </c>
-      <c r="V92" s="12" t="n">
-        <v>74.18300000000001</v>
-      </c>
-      <c r="W92" s="12" t="n">
-        <v>93.968</v>
-      </c>
-      <c r="X92" s="12" t="n">
-        <v>155.874</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="20" t="inlineStr">
         <is>
-          <t>투자유가증권 매각이익</t>
-        </is>
-      </c>
-      <c r="C93" s="22" t="n">
+          <t>외환차손</t>
+        </is>
+      </c>
+      <c r="F93" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="D93" s="22" t="n">
+      <c r="G93" s="22" t="n">
+        <v>0.637</v>
+      </c>
+      <c r="J93" s="22" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="K93" s="22" t="n">
+        <v>-0.17</v>
+      </c>
+      <c r="N93" s="22" t="n">
         <v>0</v>
-      </c>
-      <c r="E93" s="22" t="n">
-        <v>170.301</v>
-      </c>
-      <c r="F93" s="22" t="n">
-        <v>118.588</v>
-      </c>
-      <c r="G93" s="22" t="n">
-        <v>656.187</v>
-      </c>
-      <c r="H93" s="22" t="n">
-        <v>503.603</v>
-      </c>
-      <c r="I93" s="22" t="n">
-        <v>234.359</v>
-      </c>
-      <c r="J93" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K93" s="22" t="n">
-        <v>469.83</v>
-      </c>
-      <c r="L93" s="22" t="n">
-        <v>882.748</v>
-      </c>
-      <c r="M93" s="22" t="n">
-        <v>303.063</v>
-      </c>
-      <c r="V93" s="22" t="n">
-        <v>170.301</v>
-      </c>
-      <c r="W93" s="22" t="n">
-        <v>234.359</v>
-      </c>
-      <c r="X93" s="22" t="n">
-        <v>303.063</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="20" t="inlineStr">
         <is>
-          <t>신주예약권 환입이익</t>
-        </is>
-      </c>
-      <c r="C94" s="22" t="n">
-        <v>1.291</v>
-      </c>
-      <c r="D94" s="22" t="n">
-        <v>0</v>
+          <t>잡손실</t>
+        </is>
       </c>
       <c r="E94" s="22" t="n">
-        <v>0</v>
+        <v>0.534</v>
       </c>
       <c r="F94" s="22" t="n">
-        <v>0.5669999999999999</v>
-      </c>
-      <c r="G94" s="22" t="n">
-        <v>1.369</v>
-      </c>
-      <c r="H94" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I94" s="22" t="n">
-        <v>0</v>
+        <v>0.213</v>
       </c>
       <c r="J94" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="K94" s="22" t="n">
-        <v>2.556</v>
-      </c>
-      <c r="L94" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M94" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N94" s="22" t="n">
-        <v>0.281</v>
-      </c>
       <c r="T94" s="22" t="n">
         <v>0</v>
       </c>
       <c r="U94" s="22" t="n">
-        <v>0</v>
+        <v>0.884</v>
       </c>
       <c r="V94" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="W94" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="X94" s="22" t="n">
-        <v>0</v>
+        <v>0.534</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="20" t="inlineStr">
         <is>
-          <t>특별이익 합계</t>
+          <t>영업외비용 합계</t>
         </is>
       </c>
       <c r="C95" s="22" t="n">
-        <v>1.291</v>
+        <v>0</v>
       </c>
       <c r="D95" s="22" t="n">
         <v>0</v>
       </c>
       <c r="E95" s="22" t="n">
-        <v>170.302</v>
+        <v>0.534</v>
       </c>
       <c r="F95" s="22" t="n">
-        <v>119.155</v>
+        <v>0.213</v>
       </c>
       <c r="G95" s="22" t="n">
-        <v>657.556</v>
+        <v>6.572</v>
       </c>
       <c r="H95" s="22" t="n">
-        <v>503.604</v>
+        <v>31.955</v>
       </c>
       <c r="I95" s="22" t="n">
-        <v>234.358</v>
+        <v>0.477</v>
       </c>
       <c r="J95" s="22" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="K95" s="22" t="n">
+        <v>4.764</v>
+      </c>
+      <c r="L95" s="22" t="n">
+        <v>15.305</v>
+      </c>
+      <c r="M95" s="22" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="N95" s="22" t="n">
         <v>0</v>
-      </c>
-      <c r="K95" s="22" t="n">
-        <v>472.386</v>
-      </c>
-      <c r="L95" s="22" t="n">
-        <v>882.748</v>
-      </c>
-      <c r="M95" s="22" t="n">
-        <v>303.063</v>
-      </c>
-      <c r="N95" s="22" t="n">
-        <v>0.281</v>
       </c>
       <c r="T95" s="22" t="n">
         <v>0</v>
       </c>
       <c r="U95" s="22" t="n">
-        <v>6.819</v>
+        <v>0.884</v>
       </c>
       <c r="V95" s="22" t="n">
-        <v>170.302</v>
+        <v>0.534</v>
       </c>
       <c r="W95" s="22" t="n">
-        <v>234.358</v>
+        <v>0.477</v>
       </c>
       <c r="X95" s="22" t="n">
-        <v>303.063</v>
+        <v>1.58</v>
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="20" t="inlineStr">
-        <is>
-          <t>투자유가증권 매각손실</t>
-        </is>
-      </c>
-      <c r="D96" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E96" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H96" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I96" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L96" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M96" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="V96" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="W96" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="X96" s="22" t="n">
-        <v>0</v>
+      <c r="A96" s="9" t="inlineStr">
+        <is>
+          <t>경상이익</t>
+        </is>
+      </c>
+      <c r="C96" s="12" t="n">
+        <v>108.124</v>
+      </c>
+      <c r="D96" s="12" t="n">
+        <v>216.805</v>
+      </c>
+      <c r="E96" s="12" t="n">
+        <v>74.18300000000001</v>
+      </c>
+      <c r="F96" s="12" t="n">
+        <v>241.406</v>
+      </c>
+      <c r="G96" s="12" t="n">
+        <v>118.466</v>
+      </c>
+      <c r="H96" s="12" t="n">
+        <v>203.653</v>
+      </c>
+      <c r="I96" s="12" t="n">
+        <v>93.968</v>
+      </c>
+      <c r="J96" s="12" t="n">
+        <v>184.517</v>
+      </c>
+      <c r="K96" s="12" t="n">
+        <v>193.52</v>
+      </c>
+      <c r="L96" s="12" t="n">
+        <v>242.189</v>
+      </c>
+      <c r="M96" s="12" t="n">
+        <v>155.874</v>
+      </c>
+      <c r="N96" s="12" t="n">
+        <v>122.879</v>
+      </c>
+      <c r="T96" s="12" t="n">
+        <v>321.983</v>
+      </c>
+      <c r="U96" s="12" t="n">
+        <v>57.258</v>
+      </c>
+      <c r="V96" s="12" t="n">
+        <v>74.18300000000001</v>
+      </c>
+      <c r="W96" s="12" t="n">
+        <v>93.968</v>
+      </c>
+      <c r="X96" s="12" t="n">
+        <v>155.874</v>
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="20" t="inlineStr">
-        <is>
-          <t>고정자산 제각손실</t>
-        </is>
-      </c>
-      <c r="D97" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E97" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F97" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G97" s="22" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="H97" s="22" t="n">
-        <v>2.259</v>
-      </c>
-      <c r="I97" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J97" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K97" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L97" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M97" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N97" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="T97" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="U97" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="V97" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="W97" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="X97" s="22" t="n">
-        <v>0</v>
+      <c r="A97" s="45" t="inlineStr">
+        <is>
+          <t>YoY</t>
+        </is>
+      </c>
+      <c r="B97" s="3" t="inlineStr">
+        <is>
+          <t>전년 같은 분기·전년 대비</t>
+        </is>
+      </c>
+      <c r="G97" s="17">
+        <f>IF(OR(G96="",C96=""),"",IF(C96&lt;=0,"",IFERROR(G96/C96-1,"")))</f>
+        <v/>
+      </c>
+      <c r="H97" s="17">
+        <f>IF(OR(H96="",D96=""),"",IF(D96&lt;=0,"",IFERROR(H96/D96-1,"")))</f>
+        <v/>
+      </c>
+      <c r="I97" s="17">
+        <f>IF(OR(I96="",E96=""),"",IF(E96&lt;=0,"",IFERROR(I96/E96-1,"")))</f>
+        <v/>
+      </c>
+      <c r="J97" s="17">
+        <f>IF(OR(J96="",F96=""),"",IF(F96&lt;=0,"",IFERROR(J96/F96-1,"")))</f>
+        <v/>
+      </c>
+      <c r="K97" s="17">
+        <f>IF(OR(K96="",G96=""),"",IF(G96&lt;=0,"",IFERROR(K96/G96-1,"")))</f>
+        <v/>
+      </c>
+      <c r="L97" s="17">
+        <f>IF(OR(L96="",H96=""),"",IF(H96&lt;=0,"",IFERROR(L96/H96-1,"")))</f>
+        <v/>
+      </c>
+      <c r="M97" s="17">
+        <f>IF(OR(M96="",I96=""),"",IF(I96&lt;=0,"",IFERROR(M96/I96-1,"")))</f>
+        <v/>
+      </c>
+      <c r="N97" s="17">
+        <f>IF(OR(N96="",J96=""),"",IF(J96&lt;=0,"",IFERROR(N96/J96-1,"")))</f>
+        <v/>
+      </c>
+      <c r="T97" s="17">
+        <f>IF(OR(T96="",S96=""),"",IF(S96&lt;=0,"",IFERROR(T96/S96-1,"")))</f>
+        <v/>
+      </c>
+      <c r="U97" s="17">
+        <f>IF(OR(U96="",T96=""),"",IF(T96&lt;=0,"",IFERROR(U96/T96-1,"")))</f>
+        <v/>
+      </c>
+      <c r="V97" s="17">
+        <f>IF(OR(V96="",U96=""),"",IF(U96&lt;=0,"",IFERROR(V96/U96-1,"")))</f>
+        <v/>
+      </c>
+      <c r="W97" s="17">
+        <f>IF(OR(W96="",V96=""),"",IF(V96&lt;=0,"",IFERROR(W96/V96-1,"")))</f>
+        <v/>
+      </c>
+      <c r="X97" s="17">
+        <f>IF(OR(X96="",W96=""),"",IF(W96&lt;=0,"",IFERROR(X96/W96-1,"")))</f>
+        <v/>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="20" t="inlineStr">
         <is>
-          <t>특별손실 합계</t>
+          <t>투자유가증권 매각이익</t>
         </is>
       </c>
       <c r="C98" s="22" t="n">
@@ -6743,1912 +6832,2230 @@
         <v>0</v>
       </c>
       <c r="E98" s="22" t="n">
-        <v>0</v>
+        <v>170.301</v>
       </c>
       <c r="F98" s="22" t="n">
-        <v>0</v>
+        <v>118.588</v>
       </c>
       <c r="G98" s="22" t="n">
-        <v>0.511</v>
+        <v>656.187</v>
       </c>
       <c r="H98" s="22" t="n">
-        <v>2.259</v>
+        <v>503.603</v>
       </c>
       <c r="I98" s="22" t="n">
-        <v>0</v>
+        <v>234.359</v>
       </c>
       <c r="J98" s="22" t="n">
         <v>0</v>
       </c>
       <c r="K98" s="22" t="n">
+        <v>469.83</v>
+      </c>
+      <c r="L98" s="22" t="n">
+        <v>882.748</v>
+      </c>
+      <c r="M98" s="22" t="n">
+        <v>303.063</v>
+      </c>
+      <c r="V98" s="22" t="n">
+        <v>170.301</v>
+      </c>
+      <c r="W98" s="22" t="n">
+        <v>234.359</v>
+      </c>
+      <c r="X98" s="22" t="n">
+        <v>303.063</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="20" t="inlineStr">
+        <is>
+          <t>신주예약권 환입이익</t>
+        </is>
+      </c>
+      <c r="C99" s="22" t="n">
+        <v>1.291</v>
+      </c>
+      <c r="D99" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="L98" s="22" t="n">
+      <c r="E99" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="M98" s="22" t="n">
+      <c r="F99" s="22" t="n">
+        <v>0.5669999999999999</v>
+      </c>
+      <c r="G99" s="22" t="n">
+        <v>1.369</v>
+      </c>
+      <c r="H99" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="N98" s="22" t="n">
+      <c r="I99" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="T98" s="22" t="n">
+      <c r="J99" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="U98" s="22" t="n">
-        <v>-30.964</v>
-      </c>
-      <c r="V98" s="22" t="n">
+      <c r="K99" s="22" t="n">
+        <v>2.556</v>
+      </c>
+      <c r="L99" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="W98" s="22" t="n">
+      <c r="M99" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="X98" s="22" t="n">
+      <c r="N99" s="22" t="n">
+        <v>0.281</v>
+      </c>
+      <c r="T99" s="22" t="n">
         <v>0</v>
       </c>
-    </row>
-    <row r="99">
-      <c r="A99" s="9" t="inlineStr">
-        <is>
-          <t>법인세차감전 순이익</t>
-        </is>
-      </c>
-      <c r="C99" s="12" t="n">
-        <v>109.416</v>
-      </c>
-      <c r="D99" s="12" t="n">
-        <v>216.805</v>
-      </c>
-      <c r="E99" s="12" t="n">
-        <v>244.484</v>
-      </c>
-      <c r="F99" s="12" t="n">
-        <v>360.561</v>
-      </c>
-      <c r="G99" s="12" t="n">
-        <v>775.511</v>
-      </c>
-      <c r="H99" s="12" t="n">
-        <v>704.997</v>
-      </c>
-      <c r="I99" s="12" t="n">
-        <v>328.327</v>
-      </c>
-      <c r="J99" s="12" t="n">
-        <v>184.517</v>
-      </c>
-      <c r="K99" s="12" t="n">
-        <v>665.907</v>
-      </c>
-      <c r="L99" s="12" t="n">
-        <v>1124.936</v>
-      </c>
-      <c r="M99" s="12" t="n">
-        <v>458.937</v>
-      </c>
-      <c r="N99" s="12" t="n">
-        <v>123.161</v>
-      </c>
-      <c r="T99" s="12" t="n">
-        <v>321.983</v>
-      </c>
-      <c r="U99" s="12" t="n">
-        <v>95.04000000000001</v>
-      </c>
-      <c r="V99" s="12" t="n">
-        <v>244.484</v>
-      </c>
-      <c r="W99" s="12" t="n">
-        <v>328.327</v>
-      </c>
-      <c r="X99" s="12" t="n">
-        <v>458.937</v>
+      <c r="U99" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V99" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="W99" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="X99" s="22" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="20" t="inlineStr">
         <is>
-          <t>법인세·주민세·사업세</t>
+          <t>특별이익 합계</t>
         </is>
       </c>
       <c r="C100" s="22" t="n">
-        <v>41.098</v>
+        <v>1.291</v>
       </c>
       <c r="D100" s="22" t="n">
-        <v>35.464</v>
+        <v>0</v>
       </c>
       <c r="E100" s="22" t="n">
-        <v>83.173</v>
+        <v>170.302</v>
       </c>
       <c r="F100" s="22" t="n">
-        <v>76.285</v>
+        <v>119.155</v>
       </c>
       <c r="G100" s="22" t="n">
-        <v>248.231</v>
+        <v>657.556</v>
       </c>
       <c r="H100" s="22" t="n">
-        <v>190.598</v>
+        <v>503.604</v>
       </c>
       <c r="I100" s="22" t="n">
-        <v>102.618</v>
+        <v>234.358</v>
       </c>
       <c r="J100" s="22" t="n">
-        <v>9.603999999999999</v>
+        <v>0</v>
       </c>
       <c r="K100" s="22" t="n">
-        <v>197.189</v>
+        <v>472.386</v>
       </c>
       <c r="L100" s="22" t="n">
-        <v>319.374</v>
+        <v>882.748</v>
       </c>
       <c r="M100" s="22" t="n">
-        <v>120.258</v>
+        <v>303.063</v>
       </c>
       <c r="N100" s="22" t="n">
-        <v>0.675</v>
+        <v>0.281</v>
       </c>
       <c r="T100" s="22" t="n">
-        <v>118.637</v>
+        <v>0</v>
       </c>
       <c r="U100" s="22" t="n">
-        <v>19.479</v>
+        <v>6.819</v>
       </c>
       <c r="V100" s="22" t="n">
-        <v>83.173</v>
+        <v>170.302</v>
       </c>
       <c r="W100" s="22" t="n">
-        <v>102.618</v>
+        <v>234.358</v>
       </c>
       <c r="X100" s="22" t="n">
-        <v>120.258</v>
+        <v>303.063</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="20" t="inlineStr">
         <is>
-          <t>법인세 조정액</t>
-        </is>
-      </c>
-      <c r="C101" s="22" t="n">
-        <v>-14.691</v>
+          <t>투자유가증권 매각손실</t>
+        </is>
       </c>
       <c r="D101" s="22" t="n">
-        <v>12.769</v>
+        <v>0</v>
       </c>
       <c r="E101" s="22" t="n">
-        <v>-16.087</v>
-      </c>
-      <c r="F101" s="22" t="n">
-        <v>13.106</v>
-      </c>
-      <c r="G101" s="22" t="n">
-        <v>-23.591</v>
+        <v>0</v>
       </c>
       <c r="H101" s="22" t="n">
-        <v>4.693</v>
+        <v>0</v>
       </c>
       <c r="I101" s="22" t="n">
-        <v>-22.28</v>
-      </c>
-      <c r="J101" s="22" t="n">
-        <v>39.735</v>
-      </c>
-      <c r="K101" s="22" t="n">
-        <v>-20.558</v>
+        <v>0</v>
       </c>
       <c r="L101" s="22" t="n">
-        <v>-4.478</v>
+        <v>0</v>
       </c>
       <c r="M101" s="22" t="n">
-        <v>-30.807</v>
-      </c>
-      <c r="N101" s="22" t="n">
-        <v>33.962</v>
-      </c>
-      <c r="T101" s="22" t="n">
-        <v>-21.819</v>
-      </c>
-      <c r="U101" s="22" t="n">
-        <v>2.149</v>
+        <v>0</v>
       </c>
       <c r="V101" s="22" t="n">
-        <v>-16.087</v>
+        <v>0</v>
       </c>
       <c r="W101" s="22" t="n">
-        <v>-22.28</v>
+        <v>0</v>
       </c>
       <c r="X101" s="22" t="n">
-        <v>-30.807</v>
+        <v>0</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="20" t="inlineStr">
         <is>
+          <t>고정자산 제각손실</t>
+        </is>
+      </c>
+      <c r="D102" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E102" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F102" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G102" s="22" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="H102" s="22" t="n">
+        <v>2.259</v>
+      </c>
+      <c r="I102" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J102" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K102" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L102" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M102" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N102" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T102" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="U102" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V102" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="W102" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="X102" s="22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="20" t="inlineStr">
+        <is>
+          <t>특별손실 합계</t>
+        </is>
+      </c>
+      <c r="C103" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="D103" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E103" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F103" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G103" s="22" t="n">
+        <v>0.511</v>
+      </c>
+      <c r="H103" s="22" t="n">
+        <v>2.259</v>
+      </c>
+      <c r="I103" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J103" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K103" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L103" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M103" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N103" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T103" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="U103" s="22" t="n">
+        <v>-30.964</v>
+      </c>
+      <c r="V103" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="W103" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="X103" s="22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="9" t="inlineStr">
+        <is>
+          <t>법인세차감전 순이익</t>
+        </is>
+      </c>
+      <c r="C104" s="12" t="n">
+        <v>109.416</v>
+      </c>
+      <c r="D104" s="12" t="n">
+        <v>216.805</v>
+      </c>
+      <c r="E104" s="12" t="n">
+        <v>244.484</v>
+      </c>
+      <c r="F104" s="12" t="n">
+        <v>360.561</v>
+      </c>
+      <c r="G104" s="12" t="n">
+        <v>775.511</v>
+      </c>
+      <c r="H104" s="12" t="n">
+        <v>704.997</v>
+      </c>
+      <c r="I104" s="12" t="n">
+        <v>328.327</v>
+      </c>
+      <c r="J104" s="12" t="n">
+        <v>184.517</v>
+      </c>
+      <c r="K104" s="12" t="n">
+        <v>665.907</v>
+      </c>
+      <c r="L104" s="12" t="n">
+        <v>1124.936</v>
+      </c>
+      <c r="M104" s="12" t="n">
+        <v>458.937</v>
+      </c>
+      <c r="N104" s="12" t="n">
+        <v>123.161</v>
+      </c>
+      <c r="T104" s="12" t="n">
+        <v>321.983</v>
+      </c>
+      <c r="U104" s="12" t="n">
+        <v>95.04000000000001</v>
+      </c>
+      <c r="V104" s="12" t="n">
+        <v>244.484</v>
+      </c>
+      <c r="W104" s="12" t="n">
+        <v>328.327</v>
+      </c>
+      <c r="X104" s="12" t="n">
+        <v>458.937</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="20" t="inlineStr">
+        <is>
+          <t>법인세·주민세·사업세</t>
+        </is>
+      </c>
+      <c r="C105" s="22" t="n">
+        <v>41.098</v>
+      </c>
+      <c r="D105" s="22" t="n">
+        <v>35.464</v>
+      </c>
+      <c r="E105" s="22" t="n">
+        <v>83.173</v>
+      </c>
+      <c r="F105" s="22" t="n">
+        <v>76.285</v>
+      </c>
+      <c r="G105" s="22" t="n">
+        <v>248.231</v>
+      </c>
+      <c r="H105" s="22" t="n">
+        <v>190.598</v>
+      </c>
+      <c r="I105" s="22" t="n">
+        <v>102.618</v>
+      </c>
+      <c r="J105" s="22" t="n">
+        <v>9.603999999999999</v>
+      </c>
+      <c r="K105" s="22" t="n">
+        <v>197.189</v>
+      </c>
+      <c r="L105" s="22" t="n">
+        <v>319.374</v>
+      </c>
+      <c r="M105" s="22" t="n">
+        <v>120.258</v>
+      </c>
+      <c r="N105" s="22" t="n">
+        <v>0.675</v>
+      </c>
+      <c r="T105" s="22" t="n">
+        <v>118.637</v>
+      </c>
+      <c r="U105" s="22" t="n">
+        <v>19.479</v>
+      </c>
+      <c r="V105" s="22" t="n">
+        <v>83.173</v>
+      </c>
+      <c r="W105" s="22" t="n">
+        <v>102.618</v>
+      </c>
+      <c r="X105" s="22" t="n">
+        <v>120.258</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="20" t="inlineStr">
+        <is>
+          <t>법인세 조정액</t>
+        </is>
+      </c>
+      <c r="C106" s="22" t="n">
+        <v>-14.691</v>
+      </c>
+      <c r="D106" s="22" t="n">
+        <v>12.769</v>
+      </c>
+      <c r="E106" s="22" t="n">
+        <v>-16.087</v>
+      </c>
+      <c r="F106" s="22" t="n">
+        <v>13.106</v>
+      </c>
+      <c r="G106" s="22" t="n">
+        <v>-23.591</v>
+      </c>
+      <c r="H106" s="22" t="n">
+        <v>4.693</v>
+      </c>
+      <c r="I106" s="22" t="n">
+        <v>-22.28</v>
+      </c>
+      <c r="J106" s="22" t="n">
+        <v>39.735</v>
+      </c>
+      <c r="K106" s="22" t="n">
+        <v>-20.558</v>
+      </c>
+      <c r="L106" s="22" t="n">
+        <v>-4.478</v>
+      </c>
+      <c r="M106" s="22" t="n">
+        <v>-30.807</v>
+      </c>
+      <c r="N106" s="22" t="n">
+        <v>33.962</v>
+      </c>
+      <c r="T106" s="22" t="n">
+        <v>-21.819</v>
+      </c>
+      <c r="U106" s="22" t="n">
+        <v>2.149</v>
+      </c>
+      <c r="V106" s="22" t="n">
+        <v>-16.087</v>
+      </c>
+      <c r="W106" s="22" t="n">
+        <v>-22.28</v>
+      </c>
+      <c r="X106" s="22" t="n">
+        <v>-30.807</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="20" t="inlineStr">
+        <is>
           <t>법인세 등 합계</t>
         </is>
       </c>
-      <c r="C102" s="22" t="n">
+      <c r="C107" s="22" t="n">
         <v>26.406</v>
       </c>
-      <c r="D102" s="22" t="n">
+      <c r="D107" s="22" t="n">
         <v>48.233</v>
       </c>
-      <c r="E102" s="22" t="n">
+      <c r="E107" s="22" t="n">
         <v>67.086</v>
       </c>
-      <c r="F102" s="22" t="n">
+      <c r="F107" s="22" t="n">
         <v>89.392</v>
       </c>
-      <c r="G102" s="22" t="n">
+      <c r="G107" s="22" t="n">
         <v>224.638</v>
       </c>
-      <c r="H102" s="22" t="n">
+      <c r="H107" s="22" t="n">
         <v>195.292</v>
       </c>
-      <c r="I102" s="22" t="n">
+      <c r="I107" s="22" t="n">
         <v>80.33799999999999</v>
       </c>
-      <c r="J102" s="22" t="n">
+      <c r="J107" s="22" t="n">
         <v>49.339</v>
       </c>
-      <c r="K102" s="22" t="n">
+      <c r="K107" s="22" t="n">
         <v>176.632</v>
       </c>
-      <c r="L102" s="22" t="n">
+      <c r="L107" s="22" t="n">
         <v>314.896</v>
       </c>
-      <c r="M102" s="22" t="n">
+      <c r="M107" s="22" t="n">
         <v>89.449</v>
       </c>
-      <c r="N102" s="22" t="n">
+      <c r="N107" s="22" t="n">
         <v>34.637</v>
       </c>
-      <c r="T102" s="22" t="n">
+      <c r="T107" s="22" t="n">
         <v>96.818</v>
       </c>
-      <c r="U102" s="22" t="n">
+      <c r="U107" s="22" t="n">
         <v>21.628</v>
       </c>
-      <c r="V102" s="22" t="n">
+      <c r="V107" s="22" t="n">
         <v>67.086</v>
       </c>
-      <c r="W102" s="22" t="n">
+      <c r="W107" s="22" t="n">
         <v>80.33799999999999</v>
       </c>
-      <c r="X102" s="22" t="n">
+      <c r="X107" s="22" t="n">
         <v>89.449</v>
       </c>
     </row>
-    <row r="103">
-      <c r="A103" s="9" t="inlineStr">
+    <row r="108">
+      <c r="A108" s="9" t="inlineStr">
         <is>
           <t>순이익</t>
         </is>
       </c>
-      <c r="C103" s="12" t="n">
+      <c r="C108" s="12" t="n">
         <v>83.009</v>
       </c>
-      <c r="D103" s="12" t="n">
+      <c r="D108" s="12" t="n">
         <v>168.572</v>
       </c>
-      <c r="E103" s="12" t="n">
+      <c r="E108" s="12" t="n">
         <v>177.399</v>
       </c>
-      <c r="F103" s="12" t="n">
+      <c r="F108" s="12" t="n">
         <v>271.169</v>
       </c>
-      <c r="G103" s="12" t="n">
+      <c r="G108" s="12" t="n">
         <v>550.873</v>
       </c>
-      <c r="H103" s="12" t="n">
+      <c r="H108" s="12" t="n">
         <v>509.705</v>
       </c>
-      <c r="I103" s="12" t="n">
+      <c r="I108" s="12" t="n">
         <v>247.989</v>
       </c>
-      <c r="J103" s="12" t="n">
+      <c r="J108" s="12" t="n">
         <v>135.177</v>
       </c>
-      <c r="K103" s="12" t="n">
+      <c r="K108" s="12" t="n">
         <v>489.275</v>
       </c>
-      <c r="L103" s="12" t="n">
+      <c r="L108" s="12" t="n">
         <v>810.04</v>
       </c>
-      <c r="M103" s="12" t="n">
+      <c r="M108" s="12" t="n">
         <v>369.488</v>
       </c>
-      <c r="N103" s="12" t="n">
+      <c r="N108" s="12" t="n">
         <v>88.523</v>
       </c>
-      <c r="T103" s="12" t="n">
+      <c r="T108" s="12" t="n">
         <v>225.164</v>
       </c>
-      <c r="U103" s="12" t="n">
+      <c r="U108" s="12" t="n">
         <v>73.413</v>
       </c>
-      <c r="V103" s="12" t="n">
+      <c r="V108" s="12" t="n">
         <v>177.399</v>
       </c>
-      <c r="W103" s="12" t="n">
+      <c r="W108" s="12" t="n">
         <v>247.989</v>
       </c>
-      <c r="X103" s="12" t="n">
+      <c r="X108" s="12" t="n">
         <v>369.488</v>
       </c>
     </row>
-    <row r="105">
-      <c r="A105" s="18" t="inlineStr">
+    <row r="109">
+      <c r="A109" s="45" t="inlineStr">
+        <is>
+          <t>YoY</t>
+        </is>
+      </c>
+      <c r="B109" s="3" t="inlineStr">
+        <is>
+          <t>전년 같은 분기·전년 대비</t>
+        </is>
+      </c>
+      <c r="G109" s="17">
+        <f>IF(OR(G108="",C108=""),"",IF(C108&lt;=0,"",IFERROR(G108/C108-1,"")))</f>
+        <v/>
+      </c>
+      <c r="H109" s="17">
+        <f>IF(OR(H108="",D108=""),"",IF(D108&lt;=0,"",IFERROR(H108/D108-1,"")))</f>
+        <v/>
+      </c>
+      <c r="I109" s="17">
+        <f>IF(OR(I108="",E108=""),"",IF(E108&lt;=0,"",IFERROR(I108/E108-1,"")))</f>
+        <v/>
+      </c>
+      <c r="J109" s="17">
+        <f>IF(OR(J108="",F108=""),"",IF(F108&lt;=0,"",IFERROR(J108/F108-1,"")))</f>
+        <v/>
+      </c>
+      <c r="K109" s="17">
+        <f>IF(OR(K108="",G108=""),"",IF(G108&lt;=0,"",IFERROR(K108/G108-1,"")))</f>
+        <v/>
+      </c>
+      <c r="L109" s="17">
+        <f>IF(OR(L108="",H108=""),"",IF(H108&lt;=0,"",IFERROR(L108/H108-1,"")))</f>
+        <v/>
+      </c>
+      <c r="M109" s="17">
+        <f>IF(OR(M108="",I108=""),"",IF(I108&lt;=0,"",IFERROR(M108/I108-1,"")))</f>
+        <v/>
+      </c>
+      <c r="N109" s="17">
+        <f>IF(OR(N108="",J108=""),"",IF(J108&lt;=0,"",IFERROR(N108/J108-1,"")))</f>
+        <v/>
+      </c>
+      <c r="T109" s="17">
+        <f>IF(OR(T108="",S108=""),"",IF(S108&lt;=0,"",IFERROR(T108/S108-1,"")))</f>
+        <v/>
+      </c>
+      <c r="U109" s="17">
+        <f>IF(OR(U108="",T108=""),"",IF(T108&lt;=0,"",IFERROR(U108/T108-1,"")))</f>
+        <v/>
+      </c>
+      <c r="V109" s="17">
+        <f>IF(OR(V108="",U108=""),"",IF(U108&lt;=0,"",IFERROR(V108/U108-1,"")))</f>
+        <v/>
+      </c>
+      <c r="W109" s="17">
+        <f>IF(OR(W108="",V108=""),"",IF(V108&lt;=0,"",IFERROR(W108/V108-1,"")))</f>
+        <v/>
+      </c>
+      <c r="X109" s="17">
+        <f>IF(OR(X108="",W108=""),"",IF(W108&lt;=0,"",IFERROR(X108/W108-1,"")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="18" t="inlineStr">
         <is>
           <t>현금흐름표 · 전 항목</t>
         </is>
       </c>
-      <c r="B105" s="44" t="inlineStr">
+      <c r="B111" s="44" t="inlineStr">
         <is>
           <t>분기 = 결산기 첫날부터 누계(공시 그대로)</t>
         </is>
       </c>
-      <c r="C105" s="18" t="n"/>
-      <c r="D105" s="18" t="n"/>
-      <c r="E105" s="18" t="n"/>
-      <c r="F105" s="18" t="n"/>
-      <c r="G105" s="18" t="n"/>
-      <c r="H105" s="18" t="n"/>
-      <c r="I105" s="18" t="n"/>
-      <c r="J105" s="18" t="n"/>
-      <c r="K105" s="18" t="n"/>
-      <c r="L105" s="18" t="n"/>
-      <c r="M105" s="18" t="n"/>
-      <c r="N105" s="18" t="n"/>
-      <c r="O105" s="18" t="n"/>
-      <c r="P105" s="18" t="n"/>
-      <c r="Q105" s="18" t="n"/>
-      <c r="R105" s="18" t="n"/>
-      <c r="S105" s="18" t="n"/>
-      <c r="T105" s="18" t="n"/>
-      <c r="U105" s="18" t="n"/>
-      <c r="V105" s="18" t="n"/>
-      <c r="W105" s="18" t="n"/>
-      <c r="X105" s="18" t="n"/>
-      <c r="Y105" s="18" t="n"/>
-      <c r="Z105" s="18" t="n"/>
-      <c r="AA105" s="18" t="n"/>
-      <c r="AB105" s="18" t="n"/>
-      <c r="AC105" s="18" t="n"/>
-    </row>
-    <row r="106">
-      <c r="A106" s="5" t="inlineStr">
+      <c r="C111" s="18" t="n"/>
+      <c r="D111" s="18" t="n"/>
+      <c r="E111" s="18" t="n"/>
+      <c r="F111" s="18" t="n"/>
+      <c r="G111" s="18" t="n"/>
+      <c r="H111" s="18" t="n"/>
+      <c r="I111" s="18" t="n"/>
+      <c r="J111" s="18" t="n"/>
+      <c r="K111" s="18" t="n"/>
+      <c r="L111" s="18" t="n"/>
+      <c r="M111" s="18" t="n"/>
+      <c r="N111" s="18" t="n"/>
+      <c r="O111" s="18" t="n"/>
+      <c r="P111" s="18" t="n"/>
+      <c r="Q111" s="18" t="n"/>
+      <c r="R111" s="18" t="n"/>
+      <c r="S111" s="18" t="n"/>
+      <c r="T111" s="18" t="n"/>
+      <c r="U111" s="18" t="n"/>
+      <c r="V111" s="18" t="n"/>
+      <c r="W111" s="18" t="n"/>
+      <c r="X111" s="18" t="n"/>
+      <c r="Y111" s="18" t="n"/>
+      <c r="Z111" s="18" t="n"/>
+      <c r="AA111" s="18" t="n"/>
+      <c r="AB111" s="18" t="n"/>
+      <c r="AC111" s="18" t="n"/>
+    </row>
+    <row r="112">
+      <c r="A112" s="5" t="inlineStr">
         <is>
           <t>항목</t>
         </is>
       </c>
-      <c r="B106" s="5" t="inlineStr">
+      <c r="B112" s="5" t="inlineStr">
         <is>
           <t>참고</t>
         </is>
       </c>
-      <c r="C106" s="5" t="inlineStr">
+      <c r="C112" s="5" t="inlineStr">
         <is>
           <t>2024.2Q</t>
         </is>
       </c>
-      <c r="D106" s="5" t="inlineStr">
+      <c r="D112" s="5" t="inlineStr">
         <is>
           <t>2024.3Q</t>
         </is>
       </c>
-      <c r="E106" s="5" t="inlineStr">
+      <c r="E112" s="5" t="inlineStr">
         <is>
           <t>2024.4Q</t>
         </is>
       </c>
-      <c r="F106" s="5" t="inlineStr">
+      <c r="F112" s="5" t="inlineStr">
         <is>
           <t>2025.1Q</t>
         </is>
       </c>
-      <c r="G106" s="5" t="inlineStr">
+      <c r="G112" s="5" t="inlineStr">
         <is>
           <t>2025.2Q</t>
         </is>
       </c>
-      <c r="H106" s="5" t="inlineStr">
+      <c r="H112" s="5" t="inlineStr">
         <is>
           <t>2025.3Q</t>
         </is>
       </c>
-      <c r="I106" s="5" t="inlineStr">
+      <c r="I112" s="5" t="inlineStr">
         <is>
           <t>2025.4Q</t>
         </is>
       </c>
-      <c r="J106" s="5" t="inlineStr">
+      <c r="J112" s="5" t="inlineStr">
         <is>
           <t>2026.1Q</t>
         </is>
       </c>
-      <c r="K106" s="5" t="inlineStr">
+      <c r="K112" s="5" t="inlineStr">
         <is>
           <t>2026.2Q</t>
         </is>
       </c>
-      <c r="L106" s="5" t="inlineStr">
+      <c r="L112" s="5" t="inlineStr">
         <is>
           <t>2026.3Q</t>
         </is>
       </c>
-      <c r="M106" s="5" t="inlineStr">
+      <c r="M112" s="5" t="inlineStr">
         <is>
           <t>2026.4Q</t>
         </is>
       </c>
-      <c r="N106" s="5" t="inlineStr">
+      <c r="N112" s="5" t="inlineStr">
         <is>
           <t>2027.1Q</t>
         </is>
       </c>
-      <c r="O106" s="5" t="inlineStr">
+      <c r="O112" s="5" t="inlineStr">
         <is>
           <t>2017</t>
         </is>
       </c>
-      <c r="P106" s="5" t="inlineStr">
+      <c r="P112" s="5" t="inlineStr">
         <is>
           <t>2018</t>
         </is>
       </c>
-      <c r="Q106" s="5" t="inlineStr">
+      <c r="Q112" s="5" t="inlineStr">
         <is>
           <t>2019</t>
         </is>
       </c>
-      <c r="R106" s="5" t="inlineStr">
+      <c r="R112" s="5" t="inlineStr">
         <is>
           <t>2020</t>
         </is>
       </c>
-      <c r="S106" s="5" t="inlineStr">
+      <c r="S112" s="5" t="inlineStr">
         <is>
           <t>2021</t>
         </is>
       </c>
-      <c r="T106" s="5" t="inlineStr">
+      <c r="T112" s="5" t="inlineStr">
         <is>
           <t>2022</t>
         </is>
       </c>
-      <c r="U106" s="5" t="inlineStr">
+      <c r="U112" s="5" t="inlineStr">
         <is>
           <t>2023</t>
         </is>
       </c>
-      <c r="V106" s="5" t="inlineStr">
+      <c r="V112" s="5" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
       </c>
-      <c r="W106" s="5" t="inlineStr">
+      <c r="W112" s="5" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="X106" s="5" t="inlineStr">
+      <c r="X112" s="5" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="Y106" s="5" t="inlineStr">
+      <c r="Y112" s="5" t="inlineStr">
         <is>
           <t>2027(MW)</t>
         </is>
       </c>
-      <c r="Z106" s="5" t="inlineStr">
+      <c r="Z112" s="5" t="inlineStr">
         <is>
           <t>2028(MW)</t>
         </is>
       </c>
-      <c r="AA106" s="5" t="inlineStr">
+      <c r="AA112" s="5" t="inlineStr">
         <is>
           <t>2029(MW)</t>
         </is>
       </c>
-      <c r="AB106" s="5" t="inlineStr">
+      <c r="AB112" s="5" t="inlineStr">
         <is>
           <t>2030(MW)</t>
         </is>
       </c>
-      <c r="AC106" s="5" t="inlineStr">
+      <c r="AC112" s="5" t="inlineStr">
         <is>
           <t>2031(MW)</t>
         </is>
       </c>
     </row>
-    <row r="107">
-      <c r="A107" s="9" t="inlineStr">
+    <row r="113">
+      <c r="A113" s="9" t="inlineStr">
         <is>
           <t>법인세차감전 순이익</t>
         </is>
       </c>
-      <c r="E107" s="12" t="n">
+      <c r="E113" s="12" t="n">
         <v>725.2670000000001</v>
       </c>
-      <c r="I107" s="12" t="n">
+      <c r="I113" s="12" t="n">
         <v>2169.396</v>
       </c>
-      <c r="M107" s="12" t="n">
+      <c r="M113" s="12" t="n">
         <v>2434.297</v>
       </c>
-      <c r="O107" s="12" t="n">
+      <c r="O113" s="12" t="n">
         <v>1010.23</v>
       </c>
-      <c r="P107" s="12" t="n">
+      <c r="P113" s="12" t="n">
         <v>1180.901</v>
       </c>
-      <c r="Q107" s="12" t="n">
+      <c r="Q113" s="12" t="n">
         <v>1155.472</v>
       </c>
-      <c r="R107" s="12" t="n">
+      <c r="R113" s="12" t="n">
         <v>1166.334</v>
       </c>
-      <c r="S107" s="12" t="n">
+      <c r="S113" s="12" t="n">
         <v>1073.523</v>
       </c>
-      <c r="T107" s="12" t="n">
+      <c r="T113" s="12" t="n">
         <v>1340.167</v>
       </c>
-      <c r="U107" s="12" t="n">
+      <c r="U113" s="12" t="n">
         <v>764.073</v>
       </c>
-      <c r="V107" s="12" t="n">
+      <c r="V113" s="12" t="n">
         <v>725.2670000000001</v>
       </c>
-      <c r="W107" s="12" t="n">
+      <c r="W113" s="12" t="n">
         <v>2169.396</v>
       </c>
-      <c r="X107" s="12" t="n">
+      <c r="X113" s="12" t="n">
         <v>2434.297</v>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" s="20" t="inlineStr">
-        <is>
-          <t>감가상각비</t>
-        </is>
-      </c>
-      <c r="E108" s="22" t="n">
-        <v>48.694</v>
-      </c>
-      <c r="I108" s="22" t="n">
-        <v>87.09099999999999</v>
-      </c>
-      <c r="M108" s="22" t="n">
-        <v>88.245</v>
-      </c>
-      <c r="O108" s="22" t="n">
-        <v>43.747</v>
-      </c>
-      <c r="P108" s="22" t="n">
-        <v>38.318</v>
-      </c>
-      <c r="Q108" s="22" t="n">
-        <v>76.44199999999999</v>
-      </c>
-      <c r="R108" s="22" t="n">
-        <v>117.508</v>
-      </c>
-      <c r="S108" s="22" t="n">
-        <v>99.73399999999999</v>
-      </c>
-      <c r="T108" s="22" t="n">
-        <v>117.136</v>
-      </c>
-      <c r="U108" s="22" t="n">
-        <v>84.279</v>
-      </c>
-      <c r="V108" s="22" t="n">
-        <v>48.694</v>
-      </c>
-      <c r="W108" s="22" t="n">
-        <v>87.09099999999999</v>
-      </c>
-      <c r="X108" s="22" t="n">
-        <v>88.245</v>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" s="20" t="inlineStr">
-        <is>
-          <t>주식보상비용</t>
-        </is>
-      </c>
-      <c r="E109" s="22" t="n">
-        <v>19.649</v>
-      </c>
-      <c r="I109" s="22" t="n">
-        <v>20.373</v>
-      </c>
-      <c r="M109" s="22" t="n">
-        <v>25.699</v>
-      </c>
-      <c r="O109" s="22" t="n">
-        <v>26.534</v>
-      </c>
-      <c r="P109" s="22" t="n">
-        <v>29.803</v>
-      </c>
-      <c r="Q109" s="22" t="n">
-        <v>28.905</v>
-      </c>
-      <c r="R109" s="22" t="n">
-        <v>30.068</v>
-      </c>
-      <c r="S109" s="22" t="n">
-        <v>26.611</v>
-      </c>
-      <c r="T109" s="22" t="n">
-        <v>21.953</v>
-      </c>
-      <c r="U109" s="22" t="n">
-        <v>23.573</v>
-      </c>
-      <c r="V109" s="22" t="n">
-        <v>19.649</v>
-      </c>
-      <c r="W109" s="22" t="n">
-        <v>20.373</v>
-      </c>
-      <c r="X109" s="22" t="n">
-        <v>25.699</v>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" s="20" t="inlineStr">
-        <is>
-          <t>상여충당금 증감</t>
-        </is>
-      </c>
-      <c r="E110" s="22" t="n">
-        <v>1.411</v>
-      </c>
-      <c r="I110" s="22" t="n">
-        <v>13.671</v>
-      </c>
-      <c r="M110" s="22" t="n">
-        <v>20.699</v>
-      </c>
-      <c r="O110" s="22" t="n">
-        <v>1.726</v>
-      </c>
-      <c r="P110" s="22" t="n">
-        <v>5.648</v>
-      </c>
-      <c r="Q110" s="22" t="n">
-        <v>-2.498</v>
-      </c>
-      <c r="R110" s="22" t="n">
-        <v>2.282</v>
-      </c>
-      <c r="S110" s="22" t="n">
-        <v>-1.035</v>
-      </c>
-      <c r="T110" s="22" t="n">
-        <v>7.815</v>
-      </c>
-      <c r="U110" s="22" t="n">
-        <v>-11.428</v>
-      </c>
-      <c r="V110" s="22" t="n">
-        <v>1.411</v>
-      </c>
-      <c r="W110" s="22" t="n">
-        <v>13.671</v>
-      </c>
-      <c r="X110" s="22" t="n">
-        <v>20.699</v>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" s="20" t="inlineStr">
-        <is>
-          <t>대손충당금 증감</t>
-        </is>
-      </c>
-      <c r="O111" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P111" s="22" t="n">
-        <v>0.948</v>
-      </c>
-      <c r="Q111" s="22" t="n">
-        <v>-0.76</v>
-      </c>
-      <c r="R111" s="22" t="n">
-        <v>0.046</v>
-      </c>
-      <c r="S111" s="22" t="n">
-        <v>0.078</v>
-      </c>
-      <c r="T111" s="22" t="n">
-        <v>-0.313</v>
-      </c>
-      <c r="U111" s="22" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" s="20" t="inlineStr">
-        <is>
-          <t>이자·배당금 수익</t>
-        </is>
-      </c>
-      <c r="E112" s="22" t="n">
-        <v>-195.867</v>
-      </c>
-      <c r="I112" s="22" t="n">
-        <v>-191.593</v>
-      </c>
-      <c r="M112" s="22" t="n">
-        <v>-218.172</v>
-      </c>
-      <c r="O112" s="22" t="n">
-        <v>-86.786</v>
-      </c>
-      <c r="P112" s="22" t="n">
-        <v>-98.379</v>
-      </c>
-      <c r="Q112" s="22" t="n">
-        <v>-130.369</v>
-      </c>
-      <c r="R112" s="22" t="n">
-        <v>-125.463</v>
-      </c>
-      <c r="S112" s="22" t="n">
-        <v>-110.197</v>
-      </c>
-      <c r="T112" s="22" t="n">
-        <v>-130.903</v>
-      </c>
-      <c r="U112" s="22" t="n">
-        <v>-183.68</v>
-      </c>
-      <c r="V112" s="22" t="n">
-        <v>-195.867</v>
-      </c>
-      <c r="W112" s="22" t="n">
-        <v>-191.593</v>
-      </c>
-      <c r="X112" s="22" t="n">
-        <v>-218.172</v>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" s="20" t="inlineStr">
-        <is>
-          <t>고정자산 매각이익</t>
-        </is>
-      </c>
-      <c r="R113" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="S113" s="22" t="n">
-        <v>-0.24</v>
-      </c>
-      <c r="T113" s="22" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="20" t="inlineStr">
         <is>
-          <t>고정자산 제각손실</t>
+          <t>감가상각비</t>
         </is>
       </c>
       <c r="E114" s="22" t="n">
-        <v>0</v>
+        <v>48.694</v>
       </c>
       <c r="I114" s="22" t="n">
-        <v>2.274</v>
+        <v>87.09099999999999</v>
       </c>
       <c r="M114" s="22" t="n">
-        <v>0</v>
+        <v>88.245</v>
       </c>
       <c r="O114" s="22" t="n">
-        <v>2.122</v>
+        <v>43.747</v>
       </c>
       <c r="P114" s="22" t="n">
-        <v>0.004</v>
+        <v>38.318</v>
       </c>
       <c r="Q114" s="22" t="n">
-        <v>1.002</v>
+        <v>76.44199999999999</v>
       </c>
       <c r="R114" s="22" t="n">
-        <v>0.065</v>
+        <v>117.508</v>
       </c>
       <c r="S114" s="22" t="n">
-        <v>0</v>
+        <v>99.73399999999999</v>
       </c>
       <c r="T114" s="22" t="n">
-        <v>0.82</v>
+        <v>117.136</v>
       </c>
       <c r="U114" s="22" t="n">
-        <v>0</v>
+        <v>84.279</v>
       </c>
       <c r="V114" s="22" t="n">
-        <v>0</v>
+        <v>48.694</v>
       </c>
       <c r="W114" s="22" t="n">
-        <v>2.274</v>
+        <v>87.09099999999999</v>
       </c>
       <c r="X114" s="22" t="n">
-        <v>0</v>
+        <v>88.245</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="20" t="inlineStr">
         <is>
-          <t>투자유가증권 매각손익</t>
+          <t>주식보상비용</t>
         </is>
       </c>
       <c r="E115" s="22" t="n">
-        <v>-170.301</v>
+        <v>19.649</v>
       </c>
       <c r="I115" s="22" t="n">
-        <v>-1512.241</v>
+        <v>20.373</v>
       </c>
       <c r="M115" s="22" t="n">
-        <v>-1655.641</v>
+        <v>25.699</v>
+      </c>
+      <c r="O115" s="22" t="n">
+        <v>26.534</v>
+      </c>
+      <c r="P115" s="22" t="n">
+        <v>29.803</v>
+      </c>
+      <c r="Q115" s="22" t="n">
+        <v>28.905</v>
+      </c>
+      <c r="R115" s="22" t="n">
+        <v>30.068</v>
+      </c>
+      <c r="S115" s="22" t="n">
+        <v>26.611</v>
       </c>
       <c r="T115" s="22" t="n">
-        <v>0</v>
+        <v>21.953</v>
       </c>
       <c r="U115" s="22" t="n">
-        <v>-6.818</v>
+        <v>23.573</v>
       </c>
       <c r="V115" s="22" t="n">
-        <v>-170.301</v>
+        <v>19.649</v>
       </c>
       <c r="W115" s="22" t="n">
-        <v>-1512.241</v>
+        <v>20.373</v>
       </c>
       <c r="X115" s="22" t="n">
-        <v>-1655.641</v>
+        <v>25.699</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="20" t="inlineStr">
         <is>
-          <t>신주예약권 환입이익</t>
+          <t>상여충당금 증감</t>
         </is>
       </c>
       <c r="E116" s="22" t="n">
-        <v>-1.717</v>
+        <v>1.411</v>
       </c>
       <c r="I116" s="22" t="n">
-        <v>-1.936</v>
+        <v>13.671</v>
       </c>
       <c r="M116" s="22" t="n">
-        <v>-2.556</v>
+        <v>20.699</v>
       </c>
       <c r="O116" s="22" t="n">
-        <v>-9.444000000000001</v>
+        <v>1.726</v>
       </c>
       <c r="P116" s="22" t="n">
-        <v>-1.081</v>
+        <v>5.648</v>
       </c>
       <c r="Q116" s="22" t="n">
-        <v>-1.227</v>
+        <v>-2.498</v>
       </c>
       <c r="R116" s="22" t="n">
-        <v>-1.219</v>
+        <v>2.282</v>
       </c>
       <c r="S116" s="22" t="n">
-        <v>-3.504</v>
+        <v>-1.035</v>
       </c>
       <c r="T116" s="22" t="n">
-        <v>-1.158</v>
+        <v>7.815</v>
       </c>
       <c r="U116" s="22" t="n">
-        <v>-3.482</v>
+        <v>-11.428</v>
       </c>
       <c r="V116" s="22" t="n">
-        <v>-1.717</v>
+        <v>1.411</v>
       </c>
       <c r="W116" s="22" t="n">
-        <v>-1.936</v>
+        <v>13.671</v>
       </c>
       <c r="X116" s="22" t="n">
-        <v>-2.556</v>
+        <v>20.699</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="20" t="inlineStr">
         <is>
-          <t>매출채권 증감</t>
-        </is>
-      </c>
-      <c r="E117" s="22" t="n">
-        <v>-35.235</v>
-      </c>
-      <c r="I117" s="22" t="n">
-        <v>72.619</v>
-      </c>
-      <c r="M117" s="22" t="n">
-        <v>-741.1660000000001</v>
+          <t>대손충당금 증감</t>
+        </is>
       </c>
       <c r="O117" s="22" t="n">
-        <v>-261.544</v>
+        <v>0</v>
       </c>
       <c r="P117" s="22" t="n">
-        <v>-213.13</v>
+        <v>0.948</v>
       </c>
       <c r="Q117" s="22" t="n">
-        <v>187.172</v>
+        <v>-0.76</v>
       </c>
       <c r="R117" s="22" t="n">
-        <v>-390.138</v>
+        <v>0.046</v>
       </c>
       <c r="S117" s="22" t="n">
-        <v>-657.3440000000001</v>
+        <v>0.078</v>
       </c>
       <c r="T117" s="22" t="n">
-        <v>-424.492</v>
+        <v>-0.313</v>
       </c>
       <c r="U117" s="22" t="n">
-        <v>1823.044</v>
-      </c>
-      <c r="V117" s="22" t="n">
-        <v>-35.235</v>
-      </c>
-      <c r="W117" s="22" t="n">
-        <v>72.619</v>
-      </c>
-      <c r="X117" s="22" t="n">
-        <v>-741.1660000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="20" t="inlineStr">
         <is>
-          <t>재고자산 증감</t>
+          <t>이자·배당금 수익</t>
         </is>
       </c>
       <c r="E118" s="22" t="n">
-        <v>98.502</v>
+        <v>-195.867</v>
       </c>
       <c r="I118" s="22" t="n">
-        <v>-215.037</v>
+        <v>-191.593</v>
       </c>
       <c r="M118" s="22" t="n">
-        <v>-85.428</v>
+        <v>-218.172</v>
       </c>
       <c r="O118" s="22" t="n">
-        <v>-70.292</v>
+        <v>-86.786</v>
       </c>
       <c r="P118" s="22" t="n">
-        <v>-149.773</v>
+        <v>-98.379</v>
       </c>
       <c r="Q118" s="22" t="n">
-        <v>-49.931</v>
+        <v>-130.369</v>
       </c>
       <c r="R118" s="22" t="n">
-        <v>-529.188</v>
+        <v>-125.463</v>
       </c>
       <c r="S118" s="22" t="n">
-        <v>190.923</v>
+        <v>-110.197</v>
       </c>
       <c r="T118" s="22" t="n">
-        <v>-58.145</v>
+        <v>-130.903</v>
       </c>
       <c r="U118" s="22" t="n">
-        <v>414.264</v>
+        <v>-183.68</v>
       </c>
       <c r="V118" s="22" t="n">
-        <v>98.502</v>
+        <v>-195.867</v>
       </c>
       <c r="W118" s="22" t="n">
-        <v>-215.037</v>
+        <v>-191.593</v>
       </c>
       <c r="X118" s="22" t="n">
-        <v>-85.428</v>
+        <v>-218.172</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="20" t="inlineStr">
         <is>
-          <t>매입채무 증감</t>
-        </is>
-      </c>
-      <c r="E119" s="22" t="n">
-        <v>-11.783</v>
-      </c>
-      <c r="I119" s="22" t="n">
-        <v>47.554</v>
-      </c>
-      <c r="M119" s="22" t="n">
-        <v>49.756</v>
-      </c>
-      <c r="O119" s="22" t="n">
-        <v>36.713</v>
-      </c>
-      <c r="P119" s="22" t="n">
-        <v>143.472</v>
-      </c>
-      <c r="Q119" s="22" t="n">
-        <v>-40.934</v>
+          <t>고정자산 매각이익</t>
+        </is>
       </c>
       <c r="R119" s="22" t="n">
-        <v>266.902</v>
+        <v>0</v>
       </c>
       <c r="S119" s="22" t="n">
-        <v>33.591</v>
+        <v>-0.24</v>
       </c>
       <c r="T119" s="22" t="n">
-        <v>-405.9</v>
-      </c>
-      <c r="U119" s="22" t="n">
-        <v>-172.845</v>
-      </c>
-      <c r="V119" s="22" t="n">
-        <v>-11.783</v>
-      </c>
-      <c r="W119" s="22" t="n">
-        <v>47.554</v>
-      </c>
-      <c r="X119" s="22" t="n">
-        <v>49.756</v>
+        <v>0</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="20" t="inlineStr">
         <is>
-          <t>미수 소비세 증감</t>
+          <t>고정자산 제각손실</t>
         </is>
       </c>
       <c r="E120" s="22" t="n">
-        <v>139.433</v>
+        <v>0</v>
       </c>
       <c r="I120" s="22" t="n">
-        <v>26.275</v>
+        <v>2.274</v>
       </c>
       <c r="M120" s="22" t="n">
-        <v>-32.423</v>
+        <v>0</v>
+      </c>
+      <c r="O120" s="22" t="n">
+        <v>2.122</v>
+      </c>
+      <c r="P120" s="22" t="n">
+        <v>0.004</v>
       </c>
       <c r="Q120" s="22" t="n">
-        <v>19.22</v>
+        <v>1.002</v>
       </c>
       <c r="R120" s="22" t="n">
-        <v>-129.429</v>
+        <v>0.065</v>
       </c>
       <c r="S120" s="22" t="n">
-        <v>-56.203</v>
+        <v>0</v>
       </c>
       <c r="T120" s="22" t="n">
-        <v>-61.911</v>
+        <v>0.82</v>
       </c>
       <c r="U120" s="22" t="n">
-        <v>-11.106</v>
+        <v>0</v>
       </c>
       <c r="V120" s="22" t="n">
-        <v>139.433</v>
+        <v>0</v>
       </c>
       <c r="W120" s="22" t="n">
-        <v>26.275</v>
+        <v>2.274</v>
       </c>
       <c r="X120" s="22" t="n">
-        <v>-32.423</v>
+        <v>0</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="20" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>투자유가증권 매각손익</t>
         </is>
       </c>
       <c r="E121" s="22" t="n">
-        <v>-30.64</v>
+        <v>-170.301</v>
       </c>
       <c r="I121" s="22" t="n">
-        <v>63.412</v>
+        <v>-1512.241</v>
       </c>
       <c r="M121" s="22" t="n">
-        <v>-31.988</v>
-      </c>
-      <c r="O121" s="22" t="n">
-        <v>-1.738</v>
-      </c>
-      <c r="P121" s="22" t="n">
-        <v>-53.062</v>
-      </c>
-      <c r="Q121" s="22" t="n">
-        <v>4.031</v>
-      </c>
-      <c r="R121" s="22" t="n">
-        <v>8.025</v>
-      </c>
-      <c r="S121" s="22" t="n">
-        <v>-45.093</v>
+        <v>-1655.641</v>
       </c>
       <c r="T121" s="22" t="n">
-        <v>-72.514</v>
+        <v>0</v>
       </c>
       <c r="U121" s="22" t="n">
-        <v>14.625</v>
+        <v>-6.818</v>
       </c>
       <c r="V121" s="22" t="n">
-        <v>-30.64</v>
+        <v>-170.301</v>
       </c>
       <c r="W121" s="22" t="n">
-        <v>63.412</v>
+        <v>-1512.241</v>
       </c>
       <c r="X121" s="22" t="n">
-        <v>-31.988</v>
+        <v>-1655.641</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="20" t="inlineStr">
         <is>
-          <t>소계</t>
+          <t>신주예약권 환입이익</t>
         </is>
       </c>
       <c r="E122" s="22" t="n">
-        <v>587.413</v>
+        <v>-1.717</v>
       </c>
       <c r="I122" s="22" t="n">
-        <v>581.86</v>
+        <v>-1.936</v>
       </c>
       <c r="M122" s="22" t="n">
-        <v>-148.677</v>
+        <v>-2.556</v>
       </c>
       <c r="O122" s="22" t="n">
-        <v>691.266</v>
+        <v>-9.444000000000001</v>
       </c>
       <c r="P122" s="22" t="n">
-        <v>883.669</v>
+        <v>-1.081</v>
       </c>
       <c r="Q122" s="22" t="n">
-        <v>1246.526</v>
+        <v>-1.227</v>
       </c>
       <c r="R122" s="22" t="n">
-        <v>415.793</v>
+        <v>-1.219</v>
       </c>
       <c r="S122" s="22" t="n">
-        <v>550.8440000000001</v>
+        <v>-3.504</v>
       </c>
       <c r="T122" s="22" t="n">
-        <v>332.551</v>
+        <v>-1.158</v>
       </c>
       <c r="U122" s="22" t="n">
-        <v>2734.499</v>
+        <v>-3.482</v>
       </c>
       <c r="V122" s="22" t="n">
-        <v>587.413</v>
+        <v>-1.717</v>
       </c>
       <c r="W122" s="22" t="n">
-        <v>581.86</v>
+        <v>-1.936</v>
       </c>
       <c r="X122" s="22" t="n">
-        <v>-148.677</v>
+        <v>-2.556</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="20" t="inlineStr">
         <is>
-          <t>이자·배당금 수취</t>
+          <t>매출채권 증감</t>
         </is>
       </c>
       <c r="E123" s="22" t="n">
-        <v>161.74</v>
+        <v>-35.235</v>
       </c>
       <c r="I123" s="22" t="n">
-        <v>157.815</v>
+        <v>72.619</v>
       </c>
       <c r="M123" s="22" t="n">
-        <v>179.275</v>
+        <v>-741.1660000000001</v>
       </c>
       <c r="O123" s="22" t="n">
-        <v>71.315</v>
+        <v>-261.544</v>
       </c>
       <c r="P123" s="22" t="n">
-        <v>80.735</v>
+        <v>-213.13</v>
       </c>
       <c r="Q123" s="22" t="n">
-        <v>107.468</v>
+        <v>187.172</v>
       </c>
       <c r="R123" s="22" t="n">
-        <v>102.89</v>
+        <v>-390.138</v>
       </c>
       <c r="S123" s="22" t="n">
-        <v>90.047</v>
+        <v>-657.3440000000001</v>
       </c>
       <c r="T123" s="22" t="n">
-        <v>107.444</v>
+        <v>-424.492</v>
       </c>
       <c r="U123" s="22" t="n">
-        <v>150.826</v>
+        <v>1823.044</v>
       </c>
       <c r="V123" s="22" t="n">
-        <v>161.74</v>
+        <v>-35.235</v>
       </c>
       <c r="W123" s="22" t="n">
-        <v>157.815</v>
+        <v>72.619</v>
       </c>
       <c r="X123" s="22" t="n">
-        <v>179.275</v>
+        <v>-741.1660000000001</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="20" t="inlineStr">
         <is>
-          <t>법인세 납부</t>
+          <t>재고자산 증감</t>
         </is>
       </c>
       <c r="E124" s="22" t="n">
-        <v>-79.453</v>
+        <v>98.502</v>
       </c>
       <c r="I124" s="22" t="n">
-        <v>-159.887</v>
+        <v>-215.037</v>
       </c>
       <c r="M124" s="22" t="n">
-        <v>-803.173</v>
+        <v>-85.428</v>
       </c>
       <c r="O124" s="22" t="n">
-        <v>-284.086</v>
+        <v>-70.292</v>
       </c>
       <c r="P124" s="22" t="n">
-        <v>-264.973</v>
+        <v>-149.773</v>
       </c>
       <c r="Q124" s="22" t="n">
-        <v>-387.199</v>
+        <v>-49.931</v>
       </c>
       <c r="R124" s="22" t="n">
-        <v>-268.119</v>
+        <v>-529.188</v>
       </c>
       <c r="S124" s="22" t="n">
-        <v>-276.977</v>
+        <v>190.923</v>
       </c>
       <c r="T124" s="22" t="n">
-        <v>-259.987</v>
+        <v>-58.145</v>
       </c>
       <c r="U124" s="22" t="n">
-        <v>-345.683</v>
+        <v>414.264</v>
       </c>
       <c r="V124" s="22" t="n">
-        <v>-79.453</v>
+        <v>98.502</v>
       </c>
       <c r="W124" s="22" t="n">
-        <v>-159.887</v>
+        <v>-215.037</v>
       </c>
       <c r="X124" s="22" t="n">
-        <v>-803.173</v>
+        <v>-85.428</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="20" t="inlineStr">
         <is>
-          <t>법인세 환급</t>
+          <t>매입채무 증감</t>
         </is>
       </c>
       <c r="E125" s="22" t="n">
-        <v>14.979</v>
+        <v>-11.783</v>
       </c>
       <c r="I125" s="22" t="n">
-        <v>0</v>
+        <v>47.554</v>
+      </c>
+      <c r="M125" s="22" t="n">
+        <v>49.756</v>
+      </c>
+      <c r="O125" s="22" t="n">
+        <v>36.713</v>
+      </c>
+      <c r="P125" s="22" t="n">
+        <v>143.472</v>
+      </c>
+      <c r="Q125" s="22" t="n">
+        <v>-40.934</v>
+      </c>
+      <c r="R125" s="22" t="n">
+        <v>266.902</v>
+      </c>
+      <c r="S125" s="22" t="n">
+        <v>33.591</v>
+      </c>
+      <c r="T125" s="22" t="n">
+        <v>-405.9</v>
       </c>
       <c r="U125" s="22" t="n">
-        <v>0</v>
+        <v>-172.845</v>
       </c>
       <c r="V125" s="22" t="n">
-        <v>14.979</v>
+        <v>-11.783</v>
       </c>
       <c r="W125" s="22" t="n">
-        <v>0</v>
+        <v>47.554</v>
+      </c>
+      <c r="X125" s="22" t="n">
+        <v>49.756</v>
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="9" t="inlineStr">
-        <is>
-          <t>영업활동 현금흐름</t>
-        </is>
-      </c>
-      <c r="E126" s="12" t="n">
-        <v>684.6799999999999</v>
-      </c>
-      <c r="I126" s="12" t="n">
-        <v>579.789</v>
-      </c>
-      <c r="M126" s="12" t="n">
-        <v>-772.576</v>
-      </c>
-      <c r="O126" s="12" t="n">
-        <v>478.495</v>
-      </c>
-      <c r="P126" s="12" t="n">
-        <v>699.431</v>
-      </c>
-      <c r="Q126" s="12" t="n">
-        <v>966.794</v>
-      </c>
-      <c r="R126" s="12" t="n">
-        <v>250.564</v>
-      </c>
-      <c r="S126" s="12" t="n">
-        <v>363.914</v>
-      </c>
-      <c r="T126" s="12" t="n">
-        <v>180.009</v>
-      </c>
-      <c r="U126" s="12" t="n">
-        <v>2539.641</v>
-      </c>
-      <c r="V126" s="12" t="n">
-        <v>684.6799999999999</v>
-      </c>
-      <c r="W126" s="12" t="n">
-        <v>579.789</v>
-      </c>
-      <c r="X126" s="12" t="n">
-        <v>-772.576</v>
+      <c r="A126" s="20" t="inlineStr">
+        <is>
+          <t>미수 소비세 증감</t>
+        </is>
+      </c>
+      <c r="E126" s="22" t="n">
+        <v>139.433</v>
+      </c>
+      <c r="I126" s="22" t="n">
+        <v>26.275</v>
+      </c>
+      <c r="M126" s="22" t="n">
+        <v>-32.423</v>
+      </c>
+      <c r="Q126" s="22" t="n">
+        <v>19.22</v>
+      </c>
+      <c r="R126" s="22" t="n">
+        <v>-129.429</v>
+      </c>
+      <c r="S126" s="22" t="n">
+        <v>-56.203</v>
+      </c>
+      <c r="T126" s="22" t="n">
+        <v>-61.911</v>
+      </c>
+      <c r="U126" s="22" t="n">
+        <v>-11.106</v>
+      </c>
+      <c r="V126" s="22" t="n">
+        <v>139.433</v>
+      </c>
+      <c r="W126" s="22" t="n">
+        <v>26.275</v>
+      </c>
+      <c r="X126" s="22" t="n">
+        <v>-32.423</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="20" t="inlineStr">
         <is>
-          <t>유형자산 취득(설비투자)</t>
+          <t>기타</t>
         </is>
       </c>
       <c r="E127" s="22" t="n">
-        <v>-106.84</v>
+        <v>-30.64</v>
       </c>
       <c r="I127" s="22" t="n">
-        <v>-40.112</v>
+        <v>63.412</v>
       </c>
       <c r="M127" s="22" t="n">
-        <v>-69.661</v>
+        <v>-31.988</v>
       </c>
       <c r="O127" s="22" t="n">
-        <v>-17.079</v>
+        <v>-1.738</v>
       </c>
       <c r="P127" s="22" t="n">
-        <v>-29.805</v>
+        <v>-53.062</v>
       </c>
       <c r="Q127" s="22" t="n">
-        <v>-64.10299999999999</v>
+        <v>4.031</v>
       </c>
       <c r="R127" s="22" t="n">
-        <v>-117.231</v>
+        <v>8.025</v>
       </c>
       <c r="S127" s="22" t="n">
-        <v>-29.174</v>
+        <v>-45.093</v>
       </c>
       <c r="T127" s="22" t="n">
-        <v>-85.423</v>
+        <v>-72.514</v>
       </c>
       <c r="U127" s="22" t="n">
-        <v>-12.432</v>
+        <v>14.625</v>
       </c>
       <c r="V127" s="22" t="n">
-        <v>-106.84</v>
+        <v>-30.64</v>
       </c>
       <c r="W127" s="22" t="n">
-        <v>-40.112</v>
+        <v>63.412</v>
       </c>
       <c r="X127" s="22" t="n">
-        <v>-69.661</v>
+        <v>-31.988</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="20" t="inlineStr">
         <is>
-          <t>유형자산 매각</t>
-        </is>
+          <t>소계</t>
+        </is>
+      </c>
+      <c r="E128" s="22" t="n">
+        <v>587.413</v>
+      </c>
+      <c r="I128" s="22" t="n">
+        <v>581.86</v>
+      </c>
+      <c r="M128" s="22" t="n">
+        <v>-148.677</v>
+      </c>
+      <c r="O128" s="22" t="n">
+        <v>691.266</v>
+      </c>
+      <c r="P128" s="22" t="n">
+        <v>883.669</v>
+      </c>
+      <c r="Q128" s="22" t="n">
+        <v>1246.526</v>
       </c>
       <c r="R128" s="22" t="n">
-        <v>0</v>
+        <v>415.793</v>
       </c>
       <c r="S128" s="22" t="n">
-        <v>0.264</v>
+        <v>550.8440000000001</v>
       </c>
       <c r="T128" s="22" t="n">
-        <v>0</v>
+        <v>332.551</v>
+      </c>
+      <c r="U128" s="22" t="n">
+        <v>2734.499</v>
+      </c>
+      <c r="V128" s="22" t="n">
+        <v>587.413</v>
+      </c>
+      <c r="W128" s="22" t="n">
+        <v>581.86</v>
+      </c>
+      <c r="X128" s="22" t="n">
+        <v>-148.677</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="20" t="inlineStr">
         <is>
-          <t>무형자산 취득</t>
+          <t>이자·배당금 수취</t>
         </is>
       </c>
       <c r="E129" s="22" t="n">
-        <v>-25.943</v>
+        <v>161.74</v>
       </c>
       <c r="I129" s="22" t="n">
-        <v>-109.32</v>
+        <v>157.815</v>
       </c>
       <c r="M129" s="22" t="n">
-        <v>-6.856</v>
+        <v>179.275</v>
       </c>
       <c r="O129" s="22" t="n">
-        <v>-13.16</v>
+        <v>71.315</v>
       </c>
       <c r="P129" s="22" t="n">
-        <v>-129.181</v>
+        <v>80.735</v>
       </c>
       <c r="Q129" s="22" t="n">
-        <v>-16.578</v>
+        <v>107.468</v>
       </c>
       <c r="R129" s="22" t="n">
-        <v>-23.401</v>
+        <v>102.89</v>
       </c>
       <c r="S129" s="22" t="n">
-        <v>-2.027</v>
+        <v>90.047</v>
       </c>
       <c r="T129" s="22" t="n">
-        <v>0</v>
+        <v>107.444</v>
       </c>
       <c r="U129" s="22" t="n">
-        <v>-9.000999999999999</v>
+        <v>150.826</v>
       </c>
       <c r="V129" s="22" t="n">
-        <v>-25.943</v>
+        <v>161.74</v>
       </c>
       <c r="W129" s="22" t="n">
-        <v>-109.32</v>
+        <v>157.815</v>
       </c>
       <c r="X129" s="22" t="n">
-        <v>-6.856</v>
+        <v>179.275</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="20" t="inlineStr">
         <is>
-          <t>투자유가증권 취득</t>
+          <t>법인세 납부</t>
         </is>
       </c>
       <c r="E130" s="22" t="n">
-        <v>-12.38</v>
+        <v>-79.453</v>
       </c>
       <c r="I130" s="22" t="n">
-        <v>-11.88</v>
+        <v>-159.887</v>
       </c>
       <c r="M130" s="22" t="n">
-        <v>-11.88</v>
+        <v>-803.173</v>
       </c>
       <c r="O130" s="22" t="n">
-        <v>-12.462</v>
+        <v>-284.086</v>
       </c>
       <c r="P130" s="22" t="n">
-        <v>-12.48</v>
+        <v>-264.973</v>
       </c>
       <c r="Q130" s="22" t="n">
-        <v>-12.48</v>
+        <v>-387.199</v>
       </c>
       <c r="R130" s="22" t="n">
-        <v>-12.48</v>
+        <v>-268.119</v>
       </c>
       <c r="S130" s="22" t="n">
-        <v>-12.48</v>
+        <v>-276.977</v>
       </c>
       <c r="T130" s="22" t="n">
-        <v>-12.48</v>
+        <v>-259.987</v>
       </c>
       <c r="U130" s="22" t="n">
-        <v>-12.48</v>
+        <v>-345.683</v>
       </c>
       <c r="V130" s="22" t="n">
-        <v>-12.38</v>
+        <v>-79.453</v>
       </c>
       <c r="W130" s="22" t="n">
-        <v>-11.88</v>
+        <v>-159.887</v>
       </c>
       <c r="X130" s="22" t="n">
-        <v>-11.88</v>
+        <v>-803.173</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="20" t="inlineStr">
         <is>
-          <t>정기예금 인출</t>
-        </is>
-      </c>
-      <c r="O131" s="22" t="n">
+          <t>법인세 환급</t>
+        </is>
+      </c>
+      <c r="E131" s="22" t="n">
+        <v>14.979</v>
+      </c>
+      <c r="I131" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="P131" s="22" t="n">
-        <v>200.019</v>
-      </c>
-      <c r="Q131" s="22" t="n">
+      <c r="U131" s="22" t="n">
         <v>0</v>
       </c>
+      <c r="V131" s="22" t="n">
+        <v>14.979</v>
+      </c>
+      <c r="W131" s="22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="132">
-      <c r="A132" s="20" t="inlineStr">
-        <is>
-          <t>투자유가증권 매각</t>
-        </is>
-      </c>
-      <c r="E132" s="22" t="n">
-        <v>307.854</v>
-      </c>
-      <c r="I132" s="22" t="n">
-        <v>1722.768</v>
-      </c>
-      <c r="M132" s="22" t="n">
-        <v>1742.284</v>
-      </c>
-      <c r="T132" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="U132" s="22" t="n">
-        <v>47.416</v>
-      </c>
-      <c r="V132" s="22" t="n">
-        <v>307.854</v>
-      </c>
-      <c r="W132" s="22" t="n">
-        <v>1722.768</v>
-      </c>
-      <c r="X132" s="22" t="n">
-        <v>1742.284</v>
+      <c r="A132" s="9" t="inlineStr">
+        <is>
+          <t>영업활동 현금흐름</t>
+        </is>
+      </c>
+      <c r="E132" s="12" t="n">
+        <v>684.6799999999999</v>
+      </c>
+      <c r="I132" s="12" t="n">
+        <v>579.789</v>
+      </c>
+      <c r="M132" s="12" t="n">
+        <v>-772.576</v>
+      </c>
+      <c r="O132" s="12" t="n">
+        <v>478.495</v>
+      </c>
+      <c r="P132" s="12" t="n">
+        <v>699.431</v>
+      </c>
+      <c r="Q132" s="12" t="n">
+        <v>966.794</v>
+      </c>
+      <c r="R132" s="12" t="n">
+        <v>250.564</v>
+      </c>
+      <c r="S132" s="12" t="n">
+        <v>363.914</v>
+      </c>
+      <c r="T132" s="12" t="n">
+        <v>180.009</v>
+      </c>
+      <c r="U132" s="12" t="n">
+        <v>2539.641</v>
+      </c>
+      <c r="V132" s="12" t="n">
+        <v>684.6799999999999</v>
+      </c>
+      <c r="W132" s="12" t="n">
+        <v>579.789</v>
+      </c>
+      <c r="X132" s="12" t="n">
+        <v>-772.576</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="20" t="inlineStr">
         <is>
-          <t>정기예금 순증감</t>
-        </is>
+          <t>유형자산 취득(설비투자)</t>
+        </is>
+      </c>
+      <c r="E133" s="22" t="n">
+        <v>-106.84</v>
       </c>
       <c r="I133" s="22" t="n">
-        <v>0</v>
+        <v>-40.112</v>
       </c>
       <c r="M133" s="22" t="n">
-        <v>-500</v>
+        <v>-69.661</v>
+      </c>
+      <c r="O133" s="22" t="n">
+        <v>-17.079</v>
+      </c>
+      <c r="P133" s="22" t="n">
+        <v>-29.805</v>
+      </c>
+      <c r="Q133" s="22" t="n">
+        <v>-64.10299999999999</v>
+      </c>
+      <c r="R133" s="22" t="n">
+        <v>-117.231</v>
+      </c>
+      <c r="S133" s="22" t="n">
+        <v>-29.174</v>
+      </c>
+      <c r="T133" s="22" t="n">
+        <v>-85.423</v>
+      </c>
+      <c r="U133" s="22" t="n">
+        <v>-12.432</v>
+      </c>
+      <c r="V133" s="22" t="n">
+        <v>-106.84</v>
       </c>
       <c r="W133" s="22" t="n">
-        <v>0</v>
+        <v>-40.112</v>
       </c>
       <c r="X133" s="22" t="n">
-        <v>-500</v>
+        <v>-69.661</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="20" t="inlineStr">
         <is>
-          <t>임차보증금·보증금 납입</t>
-        </is>
-      </c>
-      <c r="I134" s="22" t="n">
+          <t>유형자산 매각</t>
+        </is>
+      </c>
+      <c r="R134" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="M134" s="22" t="n">
-        <v>-19.211</v>
-      </c>
-      <c r="W134" s="22" t="n">
+      <c r="S134" s="22" t="n">
+        <v>0.264</v>
+      </c>
+      <c r="T134" s="22" t="n">
         <v>0</v>
-      </c>
-      <c r="X134" s="22" t="n">
-        <v>-19.211</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="20" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>무형자산 취득</t>
         </is>
       </c>
       <c r="E135" s="22" t="n">
-        <v>4.085</v>
+        <v>-25.943</v>
       </c>
       <c r="I135" s="22" t="n">
-        <v>-38.971</v>
+        <v>-109.32</v>
       </c>
       <c r="M135" s="22" t="n">
-        <v>-20.81</v>
+        <v>-6.856</v>
       </c>
       <c r="O135" s="22" t="n">
-        <v>-1.893</v>
+        <v>-13.16</v>
       </c>
       <c r="P135" s="22" t="n">
-        <v>-0.919</v>
+        <v>-129.181</v>
       </c>
       <c r="Q135" s="22" t="n">
-        <v>2.348</v>
+        <v>-16.578</v>
       </c>
       <c r="R135" s="22" t="n">
-        <v>1.078</v>
+        <v>-23.401</v>
       </c>
       <c r="S135" s="22" t="n">
-        <v>2.733</v>
+        <v>-2.027</v>
       </c>
       <c r="T135" s="22" t="n">
-        <v>4.292</v>
+        <v>0</v>
       </c>
       <c r="U135" s="22" t="n">
-        <v>6.254</v>
+        <v>-9.000999999999999</v>
       </c>
       <c r="V135" s="22" t="n">
-        <v>4.085</v>
+        <v>-25.943</v>
       </c>
       <c r="W135" s="22" t="n">
-        <v>-38.971</v>
+        <v>-109.32</v>
       </c>
       <c r="X135" s="22" t="n">
-        <v>-20.81</v>
+        <v>-6.856</v>
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="9" t="inlineStr">
-        <is>
-          <t>투자활동 현금흐름</t>
-        </is>
-      </c>
-      <c r="E136" s="12" t="n">
-        <v>166.774</v>
-      </c>
-      <c r="I136" s="12" t="n">
-        <v>1522.484</v>
-      </c>
-      <c r="M136" s="12" t="n">
-        <v>1113.864</v>
-      </c>
-      <c r="O136" s="12" t="n">
-        <v>-44.596</v>
-      </c>
-      <c r="P136" s="12" t="n">
-        <v>27.633</v>
-      </c>
-      <c r="Q136" s="12" t="n">
-        <v>-90.812</v>
-      </c>
-      <c r="R136" s="12" t="n">
-        <v>-152.034</v>
-      </c>
-      <c r="S136" s="12" t="n">
-        <v>-40.682</v>
-      </c>
-      <c r="T136" s="12" t="n">
-        <v>-93.61</v>
-      </c>
-      <c r="U136" s="12" t="n">
-        <v>19.757</v>
-      </c>
-      <c r="V136" s="12" t="n">
-        <v>166.774</v>
-      </c>
-      <c r="W136" s="12" t="n">
-        <v>1522.484</v>
-      </c>
-      <c r="X136" s="12" t="n">
-        <v>1113.864</v>
+      <c r="A136" s="20" t="inlineStr">
+        <is>
+          <t>투자유가증권 취득</t>
+        </is>
+      </c>
+      <c r="E136" s="22" t="n">
+        <v>-12.38</v>
+      </c>
+      <c r="I136" s="22" t="n">
+        <v>-11.88</v>
+      </c>
+      <c r="M136" s="22" t="n">
+        <v>-11.88</v>
+      </c>
+      <c r="O136" s="22" t="n">
+        <v>-12.462</v>
+      </c>
+      <c r="P136" s="22" t="n">
+        <v>-12.48</v>
+      </c>
+      <c r="Q136" s="22" t="n">
+        <v>-12.48</v>
+      </c>
+      <c r="R136" s="22" t="n">
+        <v>-12.48</v>
+      </c>
+      <c r="S136" s="22" t="n">
+        <v>-12.48</v>
+      </c>
+      <c r="T136" s="22" t="n">
+        <v>-12.48</v>
+      </c>
+      <c r="U136" s="22" t="n">
+        <v>-12.48</v>
+      </c>
+      <c r="V136" s="22" t="n">
+        <v>-12.38</v>
+      </c>
+      <c r="W136" s="22" t="n">
+        <v>-11.88</v>
+      </c>
+      <c r="X136" s="22" t="n">
+        <v>-11.88</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="20" t="inlineStr">
         <is>
-          <t>자기주식 취득</t>
-        </is>
-      </c>
-      <c r="E137" s="22" t="n">
-        <v>-0.121</v>
-      </c>
-      <c r="I137" s="22" t="n">
-        <v>-0.243</v>
-      </c>
-      <c r="M137" s="22" t="n">
-        <v>-0.107</v>
+          <t>정기예금 인출</t>
+        </is>
       </c>
       <c r="O137" s="22" t="n">
-        <v>-271.205</v>
+        <v>0</v>
       </c>
       <c r="P137" s="22" t="n">
+        <v>200.019</v>
+      </c>
+      <c r="Q137" s="22" t="n">
         <v>0</v>
-      </c>
-      <c r="Q137" s="22" t="n">
-        <v>-0.094</v>
-      </c>
-      <c r="R137" s="22" t="n">
-        <v>-0.153</v>
-      </c>
-      <c r="S137" s="22" t="n">
-        <v>-0.217</v>
-      </c>
-      <c r="T137" s="22" t="n">
-        <v>-0.103</v>
-      </c>
-      <c r="U137" s="22" t="n">
-        <v>-297.718</v>
-      </c>
-      <c r="V137" s="22" t="n">
-        <v>-0.121</v>
-      </c>
-      <c r="W137" s="22" t="n">
-        <v>-0.243</v>
-      </c>
-      <c r="X137" s="22" t="n">
-        <v>-0.107</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="20" t="inlineStr">
         <is>
-          <t>자기주식 처분</t>
+          <t>투자유가증권 매각</t>
         </is>
       </c>
       <c r="E138" s="22" t="n">
-        <v>2.43</v>
+        <v>307.854</v>
       </c>
       <c r="I138" s="22" t="n">
-        <v>38.712</v>
+        <v>1722.768</v>
       </c>
       <c r="M138" s="22" t="n">
-        <v>55.412</v>
-      </c>
-      <c r="O138" s="22" t="n">
-        <v>56.994</v>
-      </c>
-      <c r="P138" s="22" t="n">
-        <v>29.301</v>
-      </c>
-      <c r="Q138" s="22" t="n">
-        <v>28.549</v>
-      </c>
-      <c r="R138" s="22" t="n">
-        <v>19.821</v>
-      </c>
-      <c r="S138" s="22" t="n">
-        <v>15.982</v>
+        <v>1742.284</v>
       </c>
       <c r="T138" s="22" t="n">
-        <v>40.573</v>
+        <v>0</v>
       </c>
       <c r="U138" s="22" t="n">
-        <v>1.222</v>
+        <v>47.416</v>
       </c>
       <c r="V138" s="22" t="n">
-        <v>2.43</v>
+        <v>307.854</v>
       </c>
       <c r="W138" s="22" t="n">
-        <v>38.712</v>
+        <v>1722.768</v>
       </c>
       <c r="X138" s="22" t="n">
-        <v>55.412</v>
+        <v>1742.284</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="20" t="inlineStr">
         <is>
-          <t>배당금 지급</t>
-        </is>
-      </c>
-      <c r="E139" s="22" t="n">
-        <v>-460.301</v>
+          <t>정기예금 순증감</t>
+        </is>
       </c>
       <c r="I139" s="22" t="n">
-        <v>-715.032</v>
+        <v>0</v>
       </c>
       <c r="M139" s="22" t="n">
-        <v>-728.373</v>
-      </c>
-      <c r="O139" s="22" t="n">
-        <v>-462.464</v>
-      </c>
-      <c r="P139" s="22" t="n">
-        <v>-459.988</v>
-      </c>
-      <c r="Q139" s="22" t="n">
-        <v>-461.14</v>
-      </c>
-      <c r="R139" s="22" t="n">
-        <v>-461.871</v>
-      </c>
-      <c r="S139" s="22" t="n">
-        <v>-462.928</v>
-      </c>
-      <c r="T139" s="22" t="n">
-        <v>-466.051</v>
-      </c>
-      <c r="U139" s="22" t="n">
-        <v>-527.554</v>
-      </c>
-      <c r="V139" s="22" t="n">
-        <v>-460.301</v>
+        <v>-500</v>
       </c>
       <c r="W139" s="22" t="n">
-        <v>-715.032</v>
+        <v>0</v>
       </c>
       <c r="X139" s="22" t="n">
-        <v>-728.373</v>
+        <v>-500</v>
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="9" t="inlineStr">
-        <is>
-          <t>재무활동 현금흐름</t>
-        </is>
-      </c>
-      <c r="E140" s="12" t="n">
-        <v>-457.992</v>
-      </c>
-      <c r="I140" s="12" t="n">
-        <v>-676.563</v>
-      </c>
-      <c r="M140" s="12" t="n">
-        <v>-673.068</v>
-      </c>
-      <c r="O140" s="12" t="n">
-        <v>-676.674</v>
-      </c>
-      <c r="P140" s="12" t="n">
-        <v>-430.686</v>
-      </c>
-      <c r="Q140" s="12" t="n">
-        <v>-432.685</v>
-      </c>
-      <c r="R140" s="12" t="n">
-        <v>-442.204</v>
-      </c>
-      <c r="S140" s="12" t="n">
-        <v>-447.163</v>
-      </c>
-      <c r="T140" s="12" t="n">
-        <v>-425.582</v>
-      </c>
-      <c r="U140" s="12" t="n">
-        <v>-824.05</v>
-      </c>
-      <c r="V140" s="12" t="n">
-        <v>-457.992</v>
-      </c>
-      <c r="W140" s="12" t="n">
-        <v>-676.563</v>
-      </c>
-      <c r="X140" s="12" t="n">
-        <v>-673.068</v>
+      <c r="A140" s="20" t="inlineStr">
+        <is>
+          <t>임차보증금·보증금 납입</t>
+        </is>
+      </c>
+      <c r="I140" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M140" s="22" t="n">
+        <v>-19.211</v>
+      </c>
+      <c r="W140" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="X140" s="22" t="n">
+        <v>-19.211</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="20" t="inlineStr">
         <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="E141" s="22" t="n">
+        <v>4.085</v>
+      </c>
+      <c r="I141" s="22" t="n">
+        <v>-38.971</v>
+      </c>
+      <c r="M141" s="22" t="n">
+        <v>-20.81</v>
+      </c>
+      <c r="O141" s="22" t="n">
+        <v>-1.893</v>
+      </c>
+      <c r="P141" s="22" t="n">
+        <v>-0.919</v>
+      </c>
+      <c r="Q141" s="22" t="n">
+        <v>2.348</v>
+      </c>
+      <c r="R141" s="22" t="n">
+        <v>1.078</v>
+      </c>
+      <c r="S141" s="22" t="n">
+        <v>2.733</v>
+      </c>
+      <c r="T141" s="22" t="n">
+        <v>4.292</v>
+      </c>
+      <c r="U141" s="22" t="n">
+        <v>6.254</v>
+      </c>
+      <c r="V141" s="22" t="n">
+        <v>4.085</v>
+      </c>
+      <c r="W141" s="22" t="n">
+        <v>-38.971</v>
+      </c>
+      <c r="X141" s="22" t="n">
+        <v>-20.81</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="9" t="inlineStr">
+        <is>
+          <t>투자활동 현금흐름</t>
+        </is>
+      </c>
+      <c r="E142" s="12" t="n">
+        <v>166.774</v>
+      </c>
+      <c r="I142" s="12" t="n">
+        <v>1522.484</v>
+      </c>
+      <c r="M142" s="12" t="n">
+        <v>1113.864</v>
+      </c>
+      <c r="O142" s="12" t="n">
+        <v>-44.596</v>
+      </c>
+      <c r="P142" s="12" t="n">
+        <v>27.633</v>
+      </c>
+      <c r="Q142" s="12" t="n">
+        <v>-90.812</v>
+      </c>
+      <c r="R142" s="12" t="n">
+        <v>-152.034</v>
+      </c>
+      <c r="S142" s="12" t="n">
+        <v>-40.682</v>
+      </c>
+      <c r="T142" s="12" t="n">
+        <v>-93.61</v>
+      </c>
+      <c r="U142" s="12" t="n">
+        <v>19.757</v>
+      </c>
+      <c r="V142" s="12" t="n">
+        <v>166.774</v>
+      </c>
+      <c r="W142" s="12" t="n">
+        <v>1522.484</v>
+      </c>
+      <c r="X142" s="12" t="n">
+        <v>1113.864</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="20" t="inlineStr">
+        <is>
+          <t>자기주식 취득</t>
+        </is>
+      </c>
+      <c r="E143" s="22" t="n">
+        <v>-0.121</v>
+      </c>
+      <c r="I143" s="22" t="n">
+        <v>-0.243</v>
+      </c>
+      <c r="M143" s="22" t="n">
+        <v>-0.107</v>
+      </c>
+      <c r="O143" s="22" t="n">
+        <v>-271.205</v>
+      </c>
+      <c r="P143" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q143" s="22" t="n">
+        <v>-0.094</v>
+      </c>
+      <c r="R143" s="22" t="n">
+        <v>-0.153</v>
+      </c>
+      <c r="S143" s="22" t="n">
+        <v>-0.217</v>
+      </c>
+      <c r="T143" s="22" t="n">
+        <v>-0.103</v>
+      </c>
+      <c r="U143" s="22" t="n">
+        <v>-297.718</v>
+      </c>
+      <c r="V143" s="22" t="n">
+        <v>-0.121</v>
+      </c>
+      <c r="W143" s="22" t="n">
+        <v>-0.243</v>
+      </c>
+      <c r="X143" s="22" t="n">
+        <v>-0.107</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="20" t="inlineStr">
+        <is>
+          <t>자기주식 처분</t>
+        </is>
+      </c>
+      <c r="E144" s="22" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="I144" s="22" t="n">
+        <v>38.712</v>
+      </c>
+      <c r="M144" s="22" t="n">
+        <v>55.412</v>
+      </c>
+      <c r="O144" s="22" t="n">
+        <v>56.994</v>
+      </c>
+      <c r="P144" s="22" t="n">
+        <v>29.301</v>
+      </c>
+      <c r="Q144" s="22" t="n">
+        <v>28.549</v>
+      </c>
+      <c r="R144" s="22" t="n">
+        <v>19.821</v>
+      </c>
+      <c r="S144" s="22" t="n">
+        <v>15.982</v>
+      </c>
+      <c r="T144" s="22" t="n">
+        <v>40.573</v>
+      </c>
+      <c r="U144" s="22" t="n">
+        <v>1.222</v>
+      </c>
+      <c r="V144" s="22" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="W144" s="22" t="n">
+        <v>38.712</v>
+      </c>
+      <c r="X144" s="22" t="n">
+        <v>55.412</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="20" t="inlineStr">
+        <is>
+          <t>배당금 지급</t>
+        </is>
+      </c>
+      <c r="E145" s="22" t="n">
+        <v>-460.301</v>
+      </c>
+      <c r="I145" s="22" t="n">
+        <v>-715.032</v>
+      </c>
+      <c r="M145" s="22" t="n">
+        <v>-728.373</v>
+      </c>
+      <c r="O145" s="22" t="n">
+        <v>-462.464</v>
+      </c>
+      <c r="P145" s="22" t="n">
+        <v>-459.988</v>
+      </c>
+      <c r="Q145" s="22" t="n">
+        <v>-461.14</v>
+      </c>
+      <c r="R145" s="22" t="n">
+        <v>-461.871</v>
+      </c>
+      <c r="S145" s="22" t="n">
+        <v>-462.928</v>
+      </c>
+      <c r="T145" s="22" t="n">
+        <v>-466.051</v>
+      </c>
+      <c r="U145" s="22" t="n">
+        <v>-527.554</v>
+      </c>
+      <c r="V145" s="22" t="n">
+        <v>-460.301</v>
+      </c>
+      <c r="W145" s="22" t="n">
+        <v>-715.032</v>
+      </c>
+      <c r="X145" s="22" t="n">
+        <v>-728.373</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="9" t="inlineStr">
+        <is>
+          <t>재무활동 현금흐름</t>
+        </is>
+      </c>
+      <c r="E146" s="12" t="n">
+        <v>-457.992</v>
+      </c>
+      <c r="I146" s="12" t="n">
+        <v>-676.563</v>
+      </c>
+      <c r="M146" s="12" t="n">
+        <v>-673.068</v>
+      </c>
+      <c r="O146" s="12" t="n">
+        <v>-676.674</v>
+      </c>
+      <c r="P146" s="12" t="n">
+        <v>-430.686</v>
+      </c>
+      <c r="Q146" s="12" t="n">
+        <v>-432.685</v>
+      </c>
+      <c r="R146" s="12" t="n">
+        <v>-442.204</v>
+      </c>
+      <c r="S146" s="12" t="n">
+        <v>-447.163</v>
+      </c>
+      <c r="T146" s="12" t="n">
+        <v>-425.582</v>
+      </c>
+      <c r="U146" s="12" t="n">
+        <v>-824.05</v>
+      </c>
+      <c r="V146" s="12" t="n">
+        <v>-457.992</v>
+      </c>
+      <c r="W146" s="12" t="n">
+        <v>-676.563</v>
+      </c>
+      <c r="X146" s="12" t="n">
+        <v>-673.068</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="20" t="inlineStr">
+        <is>
           <t>현금성자산 증감</t>
         </is>
       </c>
-      <c r="E141" s="22" t="n">
+      <c r="E147" s="22" t="n">
         <v>393.463</v>
       </c>
-      <c r="I141" s="22" t="n">
+      <c r="I147" s="22" t="n">
         <v>1425.709</v>
       </c>
-      <c r="M141" s="22" t="n">
+      <c r="M147" s="22" t="n">
         <v>-331.78</v>
       </c>
-      <c r="O141" s="22" t="n">
+      <c r="O147" s="22" t="n">
         <v>-242.775</v>
       </c>
-      <c r="P141" s="22" t="n">
+      <c r="P147" s="22" t="n">
         <v>296.378</v>
       </c>
-      <c r="Q141" s="22" t="n">
+      <c r="Q147" s="22" t="n">
         <v>443.296</v>
       </c>
-      <c r="R141" s="22" t="n">
+      <c r="R147" s="22" t="n">
         <v>-343.674</v>
       </c>
-      <c r="S141" s="22" t="n">
+      <c r="S147" s="22" t="n">
         <v>-123.931</v>
       </c>
-      <c r="T141" s="22" t="n">
+      <c r="T147" s="22" t="n">
         <v>-339.183</v>
       </c>
-      <c r="U141" s="22" t="n">
+      <c r="U147" s="22" t="n">
         <v>1735.349</v>
       </c>
-      <c r="V141" s="22" t="n">
+      <c r="V147" s="22" t="n">
         <v>393.463</v>
       </c>
-      <c r="W141" s="22" t="n">
+      <c r="W147" s="22" t="n">
         <v>1425.709</v>
       </c>
-      <c r="X141" s="22" t="n">
+      <c r="X147" s="22" t="n">
         <v>-331.78</v>
       </c>
     </row>
@@ -8689,7 +9096,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="45" t="inlineStr">
+      <c r="A2" s="46" t="inlineStr">
         <is>
           <t>재무비율은 기말 잔액 기준 · 분기 손익은 최근 4분기 합산(TTM)</t>
         </is>
@@ -10071,7 +10478,7 @@
       <c r="L42" s="25" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="46" t="inlineStr">
+      <c r="A43" s="47" t="inlineStr">
         <is>
           <t>부채비율</t>
         </is>
@@ -10123,7 +10530,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="46" t="inlineStr">
+      <c r="A44" s="47" t="inlineStr">
         <is>
           <t>순차입금비율</t>
         </is>
@@ -10175,7 +10582,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="46" t="inlineStr">
+      <c r="A45" s="47" t="inlineStr">
         <is>
           <t>자기자본비율</t>
         </is>
@@ -10227,7 +10634,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="46" t="inlineStr">
+      <c r="A46" s="47" t="inlineStr">
         <is>
           <t>유동비율</t>
         </is>
@@ -10279,7 +10686,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="46" t="inlineStr">
+      <c r="A47" s="47" t="inlineStr">
         <is>
           <t>당좌비율</t>
         </is>
@@ -10331,7 +10738,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="46" t="inlineStr">
+      <c r="A48" s="47" t="inlineStr">
         <is>
           <t>이자보상배율</t>
         </is>
@@ -10383,7 +10790,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="46" t="inlineStr">
+      <c r="A49" s="47" t="inlineStr">
         <is>
           <t>차입금 상환연수</t>
         </is>
@@ -10393,43 +10800,43 @@
           <t>4년↓ (버핏)</t>
         </is>
       </c>
-      <c r="C49" s="47">
+      <c r="C49" s="48">
         <f>IFERROR(IF((IF(COUNT('연간'!G44:J44)&lt;4,"",SUM('연간'!G44:J44)))&lt;=0,"적자",C28/(IF(COUNT('연간'!G44:J44)&lt;4,"",SUM('연간'!G44:J44)))),"")</f>
         <v/>
       </c>
-      <c r="D49" s="48">
+      <c r="D49" s="49">
         <f>IFERROR(IF((IF(COUNT('연간'!H44:K44)&lt;4,"",SUM('연간'!H44:K44)))&lt;=0,"적자",D28/(IF(COUNT('연간'!H44:K44)&lt;4,"",SUM('연간'!H44:K44)))),"")</f>
         <v/>
       </c>
-      <c r="E49" s="48">
+      <c r="E49" s="49">
         <f>IFERROR(IF((IF(COUNT('연간'!I44:L44)&lt;4,"",SUM('연간'!I44:L44)))&lt;=0,"적자",E28/(IF(COUNT('연간'!I44:L44)&lt;4,"",SUM('연간'!I44:L44)))),"")</f>
         <v/>
       </c>
-      <c r="F49" s="48">
+      <c r="F49" s="49">
         <f>IFERROR(IF((IF(COUNT('연간'!J44:M44)&lt;4,"",SUM('연간'!J44:M44)))&lt;=0,"적자",F28/(IF(COUNT('연간'!J44:M44)&lt;4,"",SUM('연간'!J44:M44)))),"")</f>
         <v/>
       </c>
-      <c r="G49" s="48">
+      <c r="G49" s="49">
         <f>IFERROR(IF((IF(COUNT('연간'!K44:N44)&lt;4,"",SUM('연간'!K44:N44)))&lt;=0,"적자",G28/(IF(COUNT('연간'!K44:N44)&lt;4,"",SUM('연간'!K44:N44)))),"")</f>
         <v/>
       </c>
-      <c r="H49" s="47">
+      <c r="H49" s="48">
         <f>IFERROR(IF(('연간'!T44)&lt;=0,"적자",H28/('연간'!T44)),"")</f>
         <v/>
       </c>
-      <c r="I49" s="48">
+      <c r="I49" s="49">
         <f>IFERROR(IF(('연간'!U44)&lt;=0,"적자",I28/('연간'!U44)),"")</f>
         <v/>
       </c>
-      <c r="J49" s="48">
+      <c r="J49" s="49">
         <f>IFERROR(IF(('연간'!V44)&lt;=0,"적자",J28/('연간'!V44)),"")</f>
         <v/>
       </c>
-      <c r="K49" s="48">
+      <c r="K49" s="49">
         <f>IFERROR(IF(('연간'!W44)&lt;=0,"적자",K28/('연간'!W44)),"")</f>
         <v/>
       </c>
-      <c r="L49" s="48">
+      <c r="L49" s="49">
         <f>IFERROR(IF(('연간'!X44)&lt;=0,"적자",L28/('연간'!X44)),"")</f>
         <v/>
       </c>
@@ -10453,7 +10860,7 @@
       <c r="L50" s="25" t="n"/>
     </row>
     <row r="51">
-      <c r="A51" s="46" t="inlineStr">
+      <c r="A51" s="47" t="inlineStr">
         <is>
           <t>ROE</t>
         </is>
@@ -10505,7 +10912,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="46" t="inlineStr">
+      <c r="A52" s="47" t="inlineStr">
         <is>
           <t>ROA</t>
         </is>
@@ -10557,7 +10964,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="46" t="inlineStr">
+      <c r="A53" s="47" t="inlineStr">
         <is>
           <t>ROIC</t>
         </is>
@@ -10609,7 +11016,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="46" t="inlineStr">
+      <c r="A54" s="47" t="inlineStr">
         <is>
           <t>매출총이익률 (GPM)</t>
         </is>
@@ -10661,7 +11068,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="46" t="inlineStr">
+      <c r="A55" s="47" t="inlineStr">
         <is>
           <t>영업이익률 (OPM)</t>
         </is>
@@ -10713,7 +11120,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="46" t="inlineStr">
+      <c r="A56" s="47" t="inlineStr">
         <is>
           <t>순이익률</t>
         </is>
@@ -10783,7 +11190,7 @@
       <c r="L57" s="25" t="n"/>
     </row>
     <row r="58">
-      <c r="A58" s="46" t="inlineStr">
+      <c r="A58" s="47" t="inlineStr">
         <is>
           <t>총자산회전율</t>
         </is>
@@ -10835,7 +11242,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="46" t="inlineStr">
+      <c r="A59" s="47" t="inlineStr">
         <is>
           <t>매출채권회전일수</t>
         </is>
@@ -10845,49 +11252,49 @@
           <t>짧을수록↑</t>
         </is>
       </c>
-      <c r="C59" s="49">
+      <c r="C59" s="50">
         <f>IFERROR(C8/(IF(COUNT('연간'!G4:J4)&lt;4,"",SUM('연간'!G4:J4)))*365,"")</f>
         <v/>
       </c>
-      <c r="D59" s="50">
+      <c r="D59" s="51">
         <f>IFERROR(D8/(IF(COUNT('연간'!H4:K4)&lt;4,"",SUM('연간'!H4:K4)))*365,"")</f>
         <v/>
       </c>
-      <c r="E59" s="50">
+      <c r="E59" s="51">
         <f>IFERROR(E8/(IF(COUNT('연간'!I4:L4)&lt;4,"",SUM('연간'!I4:L4)))*365,"")</f>
         <v/>
       </c>
-      <c r="F59" s="50">
+      <c r="F59" s="51">
         <f>IFERROR(F8/(IF(COUNT('연간'!J4:M4)&lt;4,"",SUM('연간'!J4:M4)))*365,"")</f>
         <v/>
       </c>
-      <c r="G59" s="50">
+      <c r="G59" s="51">
         <f>IFERROR(G8/(IF(COUNT('연간'!K4:N4)&lt;4,"",SUM('연간'!K4:N4)))*365,"")</f>
         <v/>
       </c>
-      <c r="H59" s="49">
+      <c r="H59" s="50">
         <f>IFERROR(H8/('연간'!T4)*365,"")</f>
         <v/>
       </c>
-      <c r="I59" s="50">
+      <c r="I59" s="51">
         <f>IFERROR(I8/('연간'!U4)*365,"")</f>
         <v/>
       </c>
-      <c r="J59" s="50">
+      <c r="J59" s="51">
         <f>IFERROR(J8/('연간'!V4)*365,"")</f>
         <v/>
       </c>
-      <c r="K59" s="50">
+      <c r="K59" s="51">
         <f>IFERROR(K8/('연간'!W4)*365,"")</f>
         <v/>
       </c>
-      <c r="L59" s="50">
+      <c r="L59" s="51">
         <f>IFERROR(L8/('연간'!X4)*365,"")</f>
         <v/>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="46" t="inlineStr">
+      <c r="A60" s="47" t="inlineStr">
         <is>
           <t>재고자산회전일수</t>
         </is>
@@ -10897,49 +11304,49 @@
           <t>짧을수록↑</t>
         </is>
       </c>
-      <c r="C60" s="49">
+      <c r="C60" s="50">
         <f>IFERROR(C9/(IF(COUNT('연간'!G11:J11)&lt;4,"",SUM('연간'!G11:J11)))*365,"")</f>
         <v/>
       </c>
-      <c r="D60" s="50">
+      <c r="D60" s="51">
         <f>IFERROR(D9/(IF(COUNT('연간'!H11:K11)&lt;4,"",SUM('연간'!H11:K11)))*365,"")</f>
         <v/>
       </c>
-      <c r="E60" s="50">
+      <c r="E60" s="51">
         <f>IFERROR(E9/(IF(COUNT('연간'!I11:L11)&lt;4,"",SUM('연간'!I11:L11)))*365,"")</f>
         <v/>
       </c>
-      <c r="F60" s="50">
+      <c r="F60" s="51">
         <f>IFERROR(F9/(IF(COUNT('연간'!J11:M11)&lt;4,"",SUM('연간'!J11:M11)))*365,"")</f>
         <v/>
       </c>
-      <c r="G60" s="50">
+      <c r="G60" s="51">
         <f>IFERROR(G9/(IF(COUNT('연간'!K11:N11)&lt;4,"",SUM('연간'!K11:N11)))*365,"")</f>
         <v/>
       </c>
-      <c r="H60" s="49">
+      <c r="H60" s="50">
         <f>IFERROR(H9/('연간'!T11)*365,"")</f>
         <v/>
       </c>
-      <c r="I60" s="50">
+      <c r="I60" s="51">
         <f>IFERROR(I9/('연간'!U11)*365,"")</f>
         <v/>
       </c>
-      <c r="J60" s="50">
+      <c r="J60" s="51">
         <f>IFERROR(J9/('연간'!V11)*365,"")</f>
         <v/>
       </c>
-      <c r="K60" s="50">
+      <c r="K60" s="51">
         <f>IFERROR(K9/('연간'!W11)*365,"")</f>
         <v/>
       </c>
-      <c r="L60" s="50">
+      <c r="L60" s="51">
         <f>IFERROR(L9/('연간'!X11)*365,"")</f>
         <v/>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="46" t="inlineStr">
+      <c r="A61" s="47" t="inlineStr">
         <is>
           <t>매입채무회전일수</t>
         </is>
@@ -10949,49 +11356,49 @@
           <t>길수록 유리</t>
         </is>
       </c>
-      <c r="C61" s="49">
+      <c r="C61" s="50">
         <f>IFERROR(C19/(IF(COUNT('연간'!G11:J11)&lt;4,"",SUM('연간'!G11:J11)))*365,"")</f>
         <v/>
       </c>
-      <c r="D61" s="50">
+      <c r="D61" s="51">
         <f>IFERROR(D19/(IF(COUNT('연간'!H11:K11)&lt;4,"",SUM('연간'!H11:K11)))*365,"")</f>
         <v/>
       </c>
-      <c r="E61" s="50">
+      <c r="E61" s="51">
         <f>IFERROR(E19/(IF(COUNT('연간'!I11:L11)&lt;4,"",SUM('연간'!I11:L11)))*365,"")</f>
         <v/>
       </c>
-      <c r="F61" s="50">
+      <c r="F61" s="51">
         <f>IFERROR(F19/(IF(COUNT('연간'!J11:M11)&lt;4,"",SUM('연간'!J11:M11)))*365,"")</f>
         <v/>
       </c>
-      <c r="G61" s="50">
+      <c r="G61" s="51">
         <f>IFERROR(G19/(IF(COUNT('연간'!K11:N11)&lt;4,"",SUM('연간'!K11:N11)))*365,"")</f>
         <v/>
       </c>
-      <c r="H61" s="49">
+      <c r="H61" s="50">
         <f>IFERROR(H19/('연간'!T11)*365,"")</f>
         <v/>
       </c>
-      <c r="I61" s="50">
+      <c r="I61" s="51">
         <f>IFERROR(I19/('연간'!U11)*365,"")</f>
         <v/>
       </c>
-      <c r="J61" s="50">
+      <c r="J61" s="51">
         <f>IFERROR(J19/('연간'!V11)*365,"")</f>
         <v/>
       </c>
-      <c r="K61" s="50">
+      <c r="K61" s="51">
         <f>IFERROR(K19/('연간'!W11)*365,"")</f>
         <v/>
       </c>
-      <c r="L61" s="50">
+      <c r="L61" s="51">
         <f>IFERROR(L19/('연간'!X11)*365,"")</f>
         <v/>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="46" t="inlineStr">
+      <c r="A62" s="47" t="inlineStr">
         <is>
           <t>현금전환주기 (CCC)</t>
         </is>
@@ -11001,43 +11408,43 @@
           <t>짧을수록↑</t>
         </is>
       </c>
-      <c r="C62" s="49">
+      <c r="C62" s="50">
         <f>IF(OR(C59="",C60="",C61=""),"",IFERROR(C59+C60-C61,""))</f>
         <v/>
       </c>
-      <c r="D62" s="50">
+      <c r="D62" s="51">
         <f>IF(OR(D59="",D60="",D61=""),"",IFERROR(D59+D60-D61,""))</f>
         <v/>
       </c>
-      <c r="E62" s="50">
+      <c r="E62" s="51">
         <f>IF(OR(E59="",E60="",E61=""),"",IFERROR(E59+E60-E61,""))</f>
         <v/>
       </c>
-      <c r="F62" s="50">
+      <c r="F62" s="51">
         <f>IF(OR(F59="",F60="",F61=""),"",IFERROR(F59+F60-F61,""))</f>
         <v/>
       </c>
-      <c r="G62" s="50">
+      <c r="G62" s="51">
         <f>IF(OR(G59="",G60="",G61=""),"",IFERROR(G59+G60-G61,""))</f>
         <v/>
       </c>
-      <c r="H62" s="49">
+      <c r="H62" s="50">
         <f>IF(OR(H59="",H60="",H61=""),"",IFERROR(H59+H60-H61,""))</f>
         <v/>
       </c>
-      <c r="I62" s="50">
+      <c r="I62" s="51">
         <f>IF(OR(I59="",I60="",I61=""),"",IFERROR(I59+I60-I61,""))</f>
         <v/>
       </c>
-      <c r="J62" s="50">
+      <c r="J62" s="51">
         <f>IF(OR(J59="",J60="",J61=""),"",IFERROR(J59+J60-J61,""))</f>
         <v/>
       </c>
-      <c r="K62" s="50">
+      <c r="K62" s="51">
         <f>IF(OR(K59="",K60="",K61=""),"",IFERROR(K59+K60-K61,""))</f>
         <v/>
       </c>
-      <c r="L62" s="50">
+      <c r="L62" s="51">
         <f>IF(OR(L59="",L60="",L61=""),"",IFERROR(L59+L60-L61,""))</f>
         <v/>
       </c>
@@ -11061,7 +11468,7 @@
       <c r="L63" s="25" t="n"/>
     </row>
     <row r="64">
-      <c r="A64" s="46" t="inlineStr">
+      <c r="A64" s="47" t="inlineStr">
         <is>
           <t>영업현금흐름 / 순이익</t>
         </is>
@@ -11113,7 +11520,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="46" t="inlineStr">
+      <c r="A65" s="47" t="inlineStr">
         <is>
           <t>FCF 마진</t>
         </is>
@@ -11165,7 +11572,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="46" t="inlineStr">
+      <c r="A66" s="47" t="inlineStr">
         <is>
           <t>CAPEX / 매출</t>
         </is>
@@ -11217,7 +11624,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="46" t="inlineStr">
+      <c r="A67" s="47" t="inlineStr">
         <is>
           <t>배당성향</t>
         </is>
@@ -13438,24 +13845,24 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="51" t="inlineStr">
+      <c r="A1" s="52" t="inlineStr">
         <is>
           <t>출처 · 쓴 결산단신</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="52" t="inlineStr">
+      <c r="A3" s="53" t="inlineStr">
         <is>
           <t>공시일</t>
         </is>
       </c>
-      <c r="B3" s="52" t="inlineStr">
+      <c r="B3" s="53" t="inlineStr">
         <is>
           <t>문서</t>
         </is>
       </c>
-      <c r="C3" s="52" t="inlineStr">
+      <c r="C3" s="53" t="inlineStr">
         <is>
           <t>PDF</t>
         </is>
